--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30524"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://feevaleedu-my.sharepoint.com/personal/0304061_feevale_br/Documents/2026-02/Projeto Inovações Tecnológicas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0304061\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="52" documentId="8_{4C5EA7DB-F6D7-44E9-90DB-29153FD41E8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2CF768A6-6AD8-4663-B89B-D36792A1CC90}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BABDCAEC-29DE-4553-8A46-F55F3A1856C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BACKLOG" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="172">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -553,13 +553,16 @@
   </si>
   <si>
     <t>Número da Issue criada no GitHub (ex.: #1, #2). Preencher após criar a Issue. Tarefas de Onda 2+ ficam com '--' até a onda ser ativada.</t>
+  </si>
+  <si>
+    <t>#26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -765,6 +768,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -783,12 +787,18 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="3">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFF0D6"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -803,13 +813,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFD6F0E0"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFF0D6"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1119,7 +1122,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H136"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1130,49 +1133,49 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1">
+    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="24"/>
-      <c r="C2" s="24"/>
-      <c r="D2" s="20" t="s">
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="21" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="24"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="18"/>
+      <c r="F2" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="24"/>
+      <c r="G2" s="18"/>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="36" customHeight="1">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="24"/>
-      <c r="C3" s="24"/>
-      <c r="D3" s="24"/>
-      <c r="E3" s="24"/>
-      <c r="F3" s="24"/>
-      <c r="G3" s="24"/>
-      <c r="H3" s="24"/>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1">
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+    </row>
+    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1198,7 +1201,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30.75">
+    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>14</v>
       </c>
@@ -1224,7 +1227,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30.75">
+    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>22</v>
       </c>
@@ -1250,7 +1253,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30.75">
+    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>27</v>
       </c>
@@ -1276,7 +1279,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30.75">
+    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>32</v>
       </c>
@@ -1302,7 +1305,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30.75">
+    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>36</v>
       </c>
@@ -1328,7 +1331,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>41</v>
       </c>
@@ -1354,7 +1357,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>44</v>
       </c>
@@ -1380,7 +1383,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>47</v>
       </c>
@@ -1406,7 +1409,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30">
+    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>51</v>
       </c>
@@ -1432,7 +1435,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="30">
+    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>56</v>
       </c>
@@ -1458,7 +1461,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>58</v>
       </c>
@@ -1480,7 +1483,7 @@
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
+    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>60</v>
       </c>
@@ -1500,13 +1503,13 @@
         <v>25</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>62</v>
       </c>
@@ -1532,7 +1535,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="15" t="s">
         <v>65</v>
       </c>
@@ -1558,7 +1561,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="15" t="s">
         <v>67</v>
       </c>
@@ -1578,13 +1581,13 @@
         <v>25</v>
       </c>
       <c r="G19" s="12" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H19" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" ht="30.75">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A20" s="15" t="s">
         <v>69</v>
       </c>
@@ -1604,13 +1607,13 @@
         <v>25</v>
       </c>
       <c r="G20" s="12" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H20" s="12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="15.95" customHeight="1">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="15" t="s">
         <v>72</v>
       </c>
@@ -1636,7 +1639,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30.75">
+    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A22" s="15" t="s">
         <v>74</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="15" t="s">
         <v>76</v>
       </c>
@@ -1688,7 +1691,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30.75">
+    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
         <v>80</v>
       </c>
@@ -1714,7 +1717,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="30.75">
+    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A25" s="15" t="s">
         <v>82</v>
       </c>
@@ -1740,7 +1743,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="15.95" customHeight="1">
+    <row r="26" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
         <v>84</v>
       </c>
@@ -1766,7 +1769,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="30.75">
+    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A27" s="15" t="s">
         <v>87</v>
       </c>
@@ -1792,7 +1795,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30.75">
+    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A28" s="15" t="s">
         <v>89</v>
       </c>
@@ -1818,7 +1821,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="30.75">
+    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A29" s="15" t="s">
         <v>91</v>
       </c>
@@ -1844,7 +1847,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27" customHeight="1">
+    <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
         <v>94</v>
       </c>
@@ -1870,7 +1873,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
         <v>96</v>
       </c>
@@ -1896,7 +1899,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="15" t="s">
         <v>98</v>
       </c>
@@ -1922,7 +1925,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30.75">
+    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A33" s="15" t="s">
         <v>102</v>
       </c>
@@ -1948,7 +1951,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30.75">
+    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A34" s="15" t="s">
         <v>104</v>
       </c>
@@ -1974,7 +1977,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A35" s="15" t="s">
         <v>106</v>
       </c>
@@ -2000,7 +2003,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30.75">
+    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A36" s="15" t="s">
         <v>108</v>
       </c>
@@ -2026,7 +2029,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A37" s="15" t="s">
         <v>111</v>
       </c>
@@ -2052,7 +2055,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="15" t="s">
         <v>113</v>
       </c>
@@ -2078,7 +2081,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
         <v>115</v>
       </c>
@@ -2104,7 +2107,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
         <v>118</v>
       </c>
@@ -2130,7 +2133,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
         <v>120</v>
       </c>
@@ -2156,7 +2159,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
         <v>122</v>
       </c>
@@ -2182,7 +2185,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
         <v>126</v>
       </c>
@@ -2208,7 +2211,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
         <v>128</v>
       </c>
@@ -2234,7 +2237,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30.75">
+    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
         <v>130</v>
       </c>
@@ -2260,7 +2263,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
         <v>133</v>
       </c>
@@ -2286,7 +2289,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
         <v>135</v>
       </c>
@@ -2312,7 +2315,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>137</v>
       </c>
@@ -2338,7 +2341,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:8">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
         <v>140</v>
       </c>
@@ -2364,7 +2367,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30.75">
+    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
         <v>142</v>
       </c>
@@ -2390,7 +2393,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:8">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A51" s="13"/>
       <c r="B51" s="13"/>
       <c r="C51" s="13"/>
@@ -2400,7 +2403,7 @@
       <c r="G51" s="14"/>
       <c r="H51" s="14"/>
     </row>
-    <row r="52" spans="1:8">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A52" s="13"/>
       <c r="B52" s="13"/>
       <c r="C52" s="13"/>
@@ -2410,7 +2413,7 @@
       <c r="G52" s="14"/>
       <c r="H52" s="14"/>
     </row>
-    <row r="53" spans="1:8">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A53" s="13"/>
       <c r="B53" s="13"/>
       <c r="C53" s="13"/>
@@ -2420,7 +2423,7 @@
       <c r="G53" s="14"/>
       <c r="H53" s="14"/>
     </row>
-    <row r="54" spans="1:8">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A54" s="13"/>
       <c r="B54" s="13"/>
       <c r="C54" s="13"/>
@@ -2430,7 +2433,7 @@
       <c r="G54" s="14"/>
       <c r="H54" s="14"/>
     </row>
-    <row r="55" spans="1:8">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A55" s="13"/>
       <c r="B55" s="13"/>
       <c r="C55" s="13"/>
@@ -2440,7 +2443,7 @@
       <c r="G55" s="14"/>
       <c r="H55" s="14"/>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A56" s="13"/>
       <c r="B56" s="13"/>
       <c r="C56" s="13"/>
@@ -2450,7 +2453,7 @@
       <c r="G56" s="14"/>
       <c r="H56" s="14"/>
     </row>
-    <row r="57" spans="1:8">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="13"/>
       <c r="B57" s="13"/>
       <c r="C57" s="13"/>
@@ -2460,7 +2463,7 @@
       <c r="G57" s="14"/>
       <c r="H57" s="14"/>
     </row>
-    <row r="58" spans="1:8">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A58" s="13"/>
       <c r="B58" s="13"/>
       <c r="C58" s="13"/>
@@ -2470,7 +2473,7 @@
       <c r="G58" s="14"/>
       <c r="H58" s="14"/>
     </row>
-    <row r="59" spans="1:8">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A59" s="13"/>
       <c r="B59" s="13"/>
       <c r="C59" s="13"/>
@@ -2480,7 +2483,7 @@
       <c r="G59" s="14"/>
       <c r="H59" s="14"/>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A60" s="13"/>
       <c r="B60" s="13"/>
       <c r="C60" s="13"/>
@@ -2490,7 +2493,7 @@
       <c r="G60" s="14"/>
       <c r="H60" s="14"/>
     </row>
-    <row r="61" spans="1:8">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A61" s="13"/>
       <c r="B61" s="13"/>
       <c r="C61" s="13"/>
@@ -2500,7 +2503,7 @@
       <c r="G61" s="14"/>
       <c r="H61" s="14"/>
     </row>
-    <row r="62" spans="1:8">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" s="13"/>
       <c r="B62" s="13"/>
       <c r="C62" s="13"/>
@@ -2510,7 +2513,7 @@
       <c r="G62" s="14"/>
       <c r="H62" s="14"/>
     </row>
-    <row r="63" spans="1:8">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" s="13"/>
       <c r="B63" s="13"/>
       <c r="C63" s="13"/>
@@ -2520,7 +2523,7 @@
       <c r="G63" s="14"/>
       <c r="H63" s="14"/>
     </row>
-    <row r="64" spans="1:8">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="13"/>
       <c r="B64" s="13"/>
       <c r="C64" s="13"/>
@@ -2530,7 +2533,7 @@
       <c r="G64" s="14"/>
       <c r="H64" s="14"/>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A65" s="13"/>
       <c r="B65" s="13"/>
       <c r="C65" s="13"/>
@@ -2540,7 +2543,7 @@
       <c r="G65" s="14"/>
       <c r="H65" s="14"/>
     </row>
-    <row r="66" spans="1:8">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="13"/>
       <c r="B66" s="13"/>
       <c r="C66" s="13"/>
@@ -2550,7 +2553,7 @@
       <c r="G66" s="14"/>
       <c r="H66" s="14"/>
     </row>
-    <row r="67" spans="1:8">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A67" s="13"/>
       <c r="B67" s="13"/>
       <c r="C67" s="13"/>
@@ -2560,7 +2563,7 @@
       <c r="G67" s="14"/>
       <c r="H67" s="14"/>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A68" s="13"/>
       <c r="B68" s="13"/>
       <c r="C68" s="13"/>
@@ -2570,7 +2573,7 @@
       <c r="G68" s="14"/>
       <c r="H68" s="14"/>
     </row>
-    <row r="69" spans="1:8">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A69" s="13"/>
       <c r="B69" s="13"/>
       <c r="C69" s="13"/>
@@ -2580,7 +2583,7 @@
       <c r="G69" s="14"/>
       <c r="H69" s="14"/>
     </row>
-    <row r="70" spans="1:8">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A70" s="13"/>
       <c r="B70" s="13"/>
       <c r="C70" s="13"/>
@@ -2590,7 +2593,7 @@
       <c r="G70" s="14"/>
       <c r="H70" s="14"/>
     </row>
-    <row r="71" spans="1:8">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A71" s="13"/>
       <c r="B71" s="13"/>
       <c r="C71" s="13"/>
@@ -2600,7 +2603,7 @@
       <c r="G71" s="14"/>
       <c r="H71" s="14"/>
     </row>
-    <row r="72" spans="1:8">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A72" s="13"/>
       <c r="B72" s="13"/>
       <c r="C72" s="13"/>
@@ -2610,7 +2613,7 @@
       <c r="G72" s="14"/>
       <c r="H72" s="14"/>
     </row>
-    <row r="73" spans="1:8">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A73" s="13"/>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -2620,7 +2623,7 @@
       <c r="G73" s="14"/>
       <c r="H73" s="14"/>
     </row>
-    <row r="74" spans="1:8">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A74" s="13"/>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
@@ -2630,7 +2633,7 @@
       <c r="G74" s="14"/>
       <c r="H74" s="14"/>
     </row>
-    <row r="75" spans="1:8">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A75" s="13"/>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
@@ -2640,7 +2643,7 @@
       <c r="G75" s="14"/>
       <c r="H75" s="14"/>
     </row>
-    <row r="76" spans="1:8">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A76" s="13"/>
       <c r="B76" s="13"/>
       <c r="C76" s="13"/>
@@ -2650,7 +2653,7 @@
       <c r="G76" s="14"/>
       <c r="H76" s="14"/>
     </row>
-    <row r="77" spans="1:8">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A77" s="13"/>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
@@ -2660,7 +2663,7 @@
       <c r="G77" s="14"/>
       <c r="H77" s="14"/>
     </row>
-    <row r="78" spans="1:8">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="13"/>
       <c r="B78" s="13"/>
       <c r="C78" s="13"/>
@@ -2670,7 +2673,7 @@
       <c r="G78" s="14"/>
       <c r="H78" s="14"/>
     </row>
-    <row r="79" spans="1:8">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A79" s="13"/>
       <c r="B79" s="13"/>
       <c r="C79" s="13"/>
@@ -2680,7 +2683,7 @@
       <c r="G79" s="14"/>
       <c r="H79" s="14"/>
     </row>
-    <row r="80" spans="1:8">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A80" s="13"/>
       <c r="B80" s="13"/>
       <c r="C80" s="13"/>
@@ -2690,7 +2693,7 @@
       <c r="G80" s="14"/>
       <c r="H80" s="14"/>
     </row>
-    <row r="81" spans="1:8">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="13"/>
       <c r="B81" s="13"/>
       <c r="C81" s="13"/>
@@ -2700,7 +2703,7 @@
       <c r="G81" s="14"/>
       <c r="H81" s="14"/>
     </row>
-    <row r="82" spans="1:8">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A82" s="13"/>
       <c r="B82" s="13"/>
       <c r="C82" s="13"/>
@@ -2710,7 +2713,7 @@
       <c r="G82" s="14"/>
       <c r="H82" s="14"/>
     </row>
-    <row r="83" spans="1:8">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="13"/>
       <c r="B83" s="13"/>
       <c r="C83" s="13"/>
@@ -2720,7 +2723,7 @@
       <c r="G83" s="14"/>
       <c r="H83" s="14"/>
     </row>
-    <row r="84" spans="1:8">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A84" s="13"/>
       <c r="B84" s="13"/>
       <c r="C84" s="13"/>
@@ -2730,7 +2733,7 @@
       <c r="G84" s="14"/>
       <c r="H84" s="14"/>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
       <c r="C85" s="13"/>
@@ -2740,7 +2743,7 @@
       <c r="G85" s="14"/>
       <c r="H85" s="14"/>
     </row>
-    <row r="86" spans="1:8">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A86" s="13"/>
       <c r="B86" s="13"/>
       <c r="C86" s="13"/>
@@ -2750,7 +2753,7 @@
       <c r="G86" s="14"/>
       <c r="H86" s="14"/>
     </row>
-    <row r="87" spans="1:8">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A87" s="13"/>
       <c r="B87" s="13"/>
       <c r="C87" s="13"/>
@@ -2760,7 +2763,7 @@
       <c r="G87" s="14"/>
       <c r="H87" s="14"/>
     </row>
-    <row r="88" spans="1:8">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="13"/>
       <c r="B88" s="13"/>
       <c r="C88" s="13"/>
@@ -2770,7 +2773,7 @@
       <c r="G88" s="14"/>
       <c r="H88" s="14"/>
     </row>
-    <row r="89" spans="1:8">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A89" s="13"/>
       <c r="B89" s="13"/>
       <c r="C89" s="13"/>
@@ -2780,7 +2783,7 @@
       <c r="G89" s="14"/>
       <c r="H89" s="14"/>
     </row>
-    <row r="90" spans="1:8">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A90" s="13"/>
       <c r="B90" s="13"/>
       <c r="C90" s="13"/>
@@ -2790,7 +2793,7 @@
       <c r="G90" s="14"/>
       <c r="H90" s="14"/>
     </row>
-    <row r="91" spans="1:8">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="13"/>
       <c r="B91" s="13"/>
       <c r="C91" s="13"/>
@@ -2800,7 +2803,7 @@
       <c r="G91" s="14"/>
       <c r="H91" s="14"/>
     </row>
-    <row r="92" spans="1:8">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A92" s="13"/>
       <c r="B92" s="13"/>
       <c r="C92" s="13"/>
@@ -2810,7 +2813,7 @@
       <c r="G92" s="14"/>
       <c r="H92" s="14"/>
     </row>
-    <row r="93" spans="1:8">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A93" s="13"/>
       <c r="B93" s="13"/>
       <c r="C93" s="13"/>
@@ -2820,7 +2823,7 @@
       <c r="G93" s="14"/>
       <c r="H93" s="14"/>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="13"/>
       <c r="B94" s="13"/>
       <c r="C94" s="13"/>
@@ -2830,7 +2833,7 @@
       <c r="G94" s="14"/>
       <c r="H94" s="14"/>
     </row>
-    <row r="95" spans="1:8">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A95" s="13"/>
       <c r="B95" s="13"/>
       <c r="C95" s="13"/>
@@ -2840,7 +2843,7 @@
       <c r="G95" s="14"/>
       <c r="H95" s="14"/>
     </row>
-    <row r="96" spans="1:8">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A96" s="13"/>
       <c r="B96" s="13"/>
       <c r="C96" s="13"/>
@@ -2850,7 +2853,7 @@
       <c r="G96" s="14"/>
       <c r="H96" s="14"/>
     </row>
-    <row r="97" spans="1:8">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A97" s="13"/>
       <c r="B97" s="13"/>
       <c r="C97" s="13"/>
@@ -2860,7 +2863,7 @@
       <c r="G97" s="14"/>
       <c r="H97" s="14"/>
     </row>
-    <row r="98" spans="1:8">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A98" s="13"/>
       <c r="B98" s="13"/>
       <c r="C98" s="13"/>
@@ -2870,7 +2873,7 @@
       <c r="G98" s="14"/>
       <c r="H98" s="14"/>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A99" s="13"/>
       <c r="B99" s="13"/>
       <c r="C99" s="13"/>
@@ -2880,7 +2883,7 @@
       <c r="G99" s="14"/>
       <c r="H99" s="14"/>
     </row>
-    <row r="100" spans="1:8">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="13"/>
       <c r="B100" s="13"/>
       <c r="C100" s="13"/>
@@ -2890,7 +2893,7 @@
       <c r="G100" s="14"/>
       <c r="H100" s="14"/>
     </row>
-    <row r="101" spans="1:8">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A101" s="13"/>
       <c r="B101" s="13"/>
       <c r="C101" s="13"/>
@@ -2900,7 +2903,7 @@
       <c r="G101" s="14"/>
       <c r="H101" s="14"/>
     </row>
-    <row r="102" spans="1:8">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A102" s="13"/>
       <c r="B102" s="13"/>
       <c r="C102" s="13"/>
@@ -2910,7 +2913,7 @@
       <c r="G102" s="14"/>
       <c r="H102" s="14"/>
     </row>
-    <row r="103" spans="1:8">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A103" s="13"/>
       <c r="B103" s="13"/>
       <c r="C103" s="13"/>
@@ -2920,7 +2923,7 @@
       <c r="G103" s="14"/>
       <c r="H103" s="14"/>
     </row>
-    <row r="104" spans="1:8">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A104" s="13"/>
       <c r="B104" s="13"/>
       <c r="C104" s="13"/>
@@ -2930,7 +2933,7 @@
       <c r="G104" s="14"/>
       <c r="H104" s="14"/>
     </row>
-    <row r="105" spans="1:8">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A105" s="13"/>
       <c r="B105" s="13"/>
       <c r="C105" s="13"/>
@@ -2940,7 +2943,7 @@
       <c r="G105" s="14"/>
       <c r="H105" s="14"/>
     </row>
-    <row r="106" spans="1:8">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A106" s="13"/>
       <c r="B106" s="13"/>
       <c r="C106" s="13"/>
@@ -2950,7 +2953,7 @@
       <c r="G106" s="14"/>
       <c r="H106" s="14"/>
     </row>
-    <row r="107" spans="1:8">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A107" s="13"/>
       <c r="B107" s="13"/>
       <c r="C107" s="13"/>
@@ -2960,7 +2963,7 @@
       <c r="G107" s="14"/>
       <c r="H107" s="14"/>
     </row>
-    <row r="108" spans="1:8">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A108" s="13"/>
       <c r="B108" s="13"/>
       <c r="C108" s="13"/>
@@ -2970,7 +2973,7 @@
       <c r="G108" s="14"/>
       <c r="H108" s="14"/>
     </row>
-    <row r="109" spans="1:8">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="13"/>
       <c r="B109" s="13"/>
       <c r="C109" s="13"/>
@@ -2980,7 +2983,7 @@
       <c r="G109" s="14"/>
       <c r="H109" s="14"/>
     </row>
-    <row r="110" spans="1:8">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A110" s="13"/>
       <c r="B110" s="13"/>
       <c r="C110" s="13"/>
@@ -2990,7 +2993,7 @@
       <c r="G110" s="14"/>
       <c r="H110" s="14"/>
     </row>
-    <row r="111" spans="1:8">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="13"/>
       <c r="B111" s="13"/>
       <c r="C111" s="13"/>
@@ -3000,7 +3003,7 @@
       <c r="G111" s="14"/>
       <c r="H111" s="14"/>
     </row>
-    <row r="112" spans="1:8">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A112" s="13"/>
       <c r="B112" s="13"/>
       <c r="C112" s="13"/>
@@ -3010,7 +3013,7 @@
       <c r="G112" s="14"/>
       <c r="H112" s="14"/>
     </row>
-    <row r="113" spans="1:8">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A113" s="13"/>
       <c r="B113" s="13"/>
       <c r="C113" s="13"/>
@@ -3020,7 +3023,7 @@
       <c r="G113" s="14"/>
       <c r="H113" s="14"/>
     </row>
-    <row r="114" spans="1:8">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A114" s="13"/>
       <c r="B114" s="13"/>
       <c r="C114" s="13"/>
@@ -3030,7 +3033,7 @@
       <c r="G114" s="14"/>
       <c r="H114" s="14"/>
     </row>
-    <row r="115" spans="1:8">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A115" s="13"/>
       <c r="B115" s="13"/>
       <c r="C115" s="13"/>
@@ -3040,7 +3043,7 @@
       <c r="G115" s="14"/>
       <c r="H115" s="14"/>
     </row>
-    <row r="116" spans="1:8">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A116" s="13"/>
       <c r="B116" s="13"/>
       <c r="C116" s="13"/>
@@ -3050,7 +3053,7 @@
       <c r="G116" s="14"/>
       <c r="H116" s="14"/>
     </row>
-    <row r="117" spans="1:8">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A117" s="13"/>
       <c r="B117" s="13"/>
       <c r="C117" s="13"/>
@@ -3060,7 +3063,7 @@
       <c r="G117" s="14"/>
       <c r="H117" s="14"/>
     </row>
-    <row r="118" spans="1:8">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A118" s="13"/>
       <c r="B118" s="13"/>
       <c r="C118" s="13"/>
@@ -3070,7 +3073,7 @@
       <c r="G118" s="14"/>
       <c r="H118" s="14"/>
     </row>
-    <row r="119" spans="1:8">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A119" s="13"/>
       <c r="B119" s="13"/>
       <c r="C119" s="13"/>
@@ -3080,7 +3083,7 @@
       <c r="G119" s="14"/>
       <c r="H119" s="14"/>
     </row>
-    <row r="120" spans="1:8">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
       <c r="B120" s="13"/>
       <c r="C120" s="13"/>
@@ -3090,7 +3093,7 @@
       <c r="G120" s="14"/>
       <c r="H120" s="14"/>
     </row>
-    <row r="121" spans="1:8">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A121" s="13"/>
       <c r="B121" s="13"/>
       <c r="C121" s="13"/>
@@ -3100,7 +3103,7 @@
       <c r="G121" s="14"/>
       <c r="H121" s="14"/>
     </row>
-    <row r="122" spans="1:8">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A122" s="13"/>
       <c r="B122" s="13"/>
       <c r="C122" s="13"/>
@@ -3110,7 +3113,7 @@
       <c r="G122" s="14"/>
       <c r="H122" s="14"/>
     </row>
-    <row r="123" spans="1:8">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="13"/>
       <c r="B123" s="13"/>
       <c r="C123" s="13"/>
@@ -3120,7 +3123,7 @@
       <c r="G123" s="14"/>
       <c r="H123" s="14"/>
     </row>
-    <row r="124" spans="1:8">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A124" s="13"/>
       <c r="B124" s="13"/>
       <c r="C124" s="13"/>
@@ -3130,7 +3133,7 @@
       <c r="G124" s="14"/>
       <c r="H124" s="14"/>
     </row>
-    <row r="125" spans="1:8">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A125" s="13"/>
       <c r="B125" s="13"/>
       <c r="C125" s="13"/>
@@ -3140,7 +3143,7 @@
       <c r="G125" s="14"/>
       <c r="H125" s="14"/>
     </row>
-    <row r="126" spans="1:8">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A126" s="13"/>
       <c r="B126" s="13"/>
       <c r="C126" s="13"/>
@@ -3150,7 +3153,7 @@
       <c r="G126" s="14"/>
       <c r="H126" s="14"/>
     </row>
-    <row r="127" spans="1:8">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A127" s="13"/>
       <c r="B127" s="13"/>
       <c r="C127" s="13"/>
@@ -3160,7 +3163,7 @@
       <c r="G127" s="14"/>
       <c r="H127" s="14"/>
     </row>
-    <row r="128" spans="1:8">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="13"/>
       <c r="B128" s="13"/>
       <c r="C128" s="13"/>
@@ -3170,7 +3173,7 @@
       <c r="G128" s="14"/>
       <c r="H128" s="14"/>
     </row>
-    <row r="129" spans="1:8">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A129" s="13"/>
       <c r="B129" s="13"/>
       <c r="C129" s="13"/>
@@ -3180,7 +3183,7 @@
       <c r="G129" s="14"/>
       <c r="H129" s="14"/>
     </row>
-    <row r="130" spans="1:8">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="13"/>
       <c r="B130" s="13"/>
       <c r="C130" s="13"/>
@@ -3190,7 +3193,7 @@
       <c r="G130" s="14"/>
       <c r="H130" s="14"/>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A131" s="13"/>
       <c r="B131" s="13"/>
       <c r="C131" s="13"/>
@@ -3200,7 +3203,7 @@
       <c r="G131" s="14"/>
       <c r="H131" s="14"/>
     </row>
-    <row r="132" spans="1:8">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A132" s="13"/>
       <c r="B132" s="13"/>
       <c r="C132" s="13"/>
@@ -3210,7 +3213,7 @@
       <c r="G132" s="14"/>
       <c r="H132" s="14"/>
     </row>
-    <row r="133" spans="1:8">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A133" s="13"/>
       <c r="B133" s="13"/>
       <c r="C133" s="13"/>
@@ -3220,7 +3223,7 @@
       <c r="G133" s="14"/>
       <c r="H133" s="14"/>
     </row>
-    <row r="134" spans="1:8">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A134" s="13"/>
       <c r="B134" s="13"/>
       <c r="C134" s="13"/>
@@ -3230,7 +3233,7 @@
       <c r="G134" s="14"/>
       <c r="H134" s="14"/>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="13"/>
       <c r="B135" s="13"/>
       <c r="C135" s="13"/>
@@ -3240,7 +3243,7 @@
       <c r="G135" s="14"/>
       <c r="H135" s="14"/>
     </row>
-    <row r="136" spans="1:8">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A136" s="13"/>
       <c r="B136" s="13"/>
       <c r="C136" s="13"/>
@@ -3264,17 +3267,17 @@
     <mergeCell ref="D2:E2"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
-  <conditionalFormatting sqref="B23:H50">
-    <cfRule type="expression" dxfId="2" priority="1">
-      <formula>AND($B23&lt;&gt;"Onda 2", $H23="--")</formula>
+  <conditionalFormatting sqref="A5:H50">
+    <cfRule type="expression" dxfId="2" priority="5">
+      <formula>$B5="Onda 2"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="7">
+      <formula>$H5&lt;&gt;"--"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A5:H50">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>$B5="Onda 2"</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="7">
-      <formula>$H5&lt;&gt;"--"</formula>
+  <conditionalFormatting sqref="B23:H50">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>AND($B23&lt;&gt;"Onda 2", $H23="--")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
@@ -3301,19 +3304,19 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1">
-      <c r="A1" s="21" t="s">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="24"/>
-    </row>
-    <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1">
+      <c r="B1" s="18"/>
+    </row>
+    <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
         <v>145</v>
       </c>
@@ -3321,7 +3324,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="9" t="s">
         <v>147</v>
       </c>
@@ -3329,7 +3332,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>149</v>
       </c>
@@ -3337,7 +3340,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="9" t="s">
         <v>151</v>
       </c>
@@ -3345,7 +3348,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>153</v>
       </c>
@@ -3353,7 +3356,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="9" t="s">
         <v>155</v>
       </c>
@@ -3361,7 +3364,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
         <v>157</v>
       </c>
@@ -3369,7 +3372,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="9" t="s">
         <v>159</v>
       </c>
@@ -3377,7 +3380,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
+    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
         <v>161</v>
       </c>
@@ -3385,107 +3388,107 @@
         <v>162</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="23" t="s">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A12" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="24"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="24"/>
-      <c r="E12" s="24"/>
-      <c r="F12" s="24"/>
-      <c r="G12" s="24"/>
-      <c r="H12" s="24"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="B12" s="18"/>
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="22" t="s">
+      <c r="B13" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="24"/>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" s="24"/>
-      <c r="G13" s="24"/>
-      <c r="H13" s="24"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="18"/>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="22" t="s">
+      <c r="B14" s="23" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="24"/>
-      <c r="D14" s="24"/>
-      <c r="E14" s="24"/>
-      <c r="F14" s="24"/>
-      <c r="G14" s="24"/>
-      <c r="H14" s="24"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="18"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="22" t="s">
+      <c r="B15" s="23" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="24"/>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" s="24"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
-    </row>
-    <row r="17" spans="1:8">
-      <c r="A17" s="23" t="s">
+      <c r="C15" s="18"/>
+      <c r="D15" s="18"/>
+      <c r="E15" s="18"/>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A17" s="24" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="24"/>
-      <c r="C17" s="24"/>
-      <c r="D17" s="24"/>
-      <c r="E17" s="24"/>
-      <c r="F17" s="24"/>
-      <c r="G17" s="24"/>
-      <c r="H17" s="24"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="B17" s="18"/>
+      <c r="C17" s="18"/>
+      <c r="D17" s="18"/>
+      <c r="E17" s="18"/>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="22" t="s">
+      <c r="B18" s="23" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="24"/>
-      <c r="D18" s="24"/>
-      <c r="E18" s="24"/>
-      <c r="F18" s="24"/>
-      <c r="G18" s="24"/>
-      <c r="H18" s="24"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="22" t="s">
+      <c r="B19" s="23" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="24"/>
-      <c r="D19" s="24"/>
-      <c r="E19" s="24"/>
-      <c r="F19" s="24"/>
-      <c r="G19" s="24"/>
-      <c r="H19" s="24"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="C19" s="18"/>
+      <c r="D19" s="18"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="22" t="s">
+      <c r="B20" s="23" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="24"/>
-      <c r="D20" s="24"/>
-      <c r="E20" s="24"/>
-      <c r="F20" s="24"/>
-      <c r="G20" s="24"/>
-      <c r="H20" s="24"/>
+      <c r="C20" s="18"/>
+      <c r="D20" s="18"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3505,20 +3508,20 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3730,13 +3733,37 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0304061\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BABDCAEC-29DE-4553-8A46-F55F3A1856C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A2E334-1F59-4799-9EFB-139A1607ECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="410" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="173">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -556,13 +556,16 @@
   </si>
   <si>
     <t>#26</t>
+  </si>
+  <si>
+    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -634,13 +637,6 @@
     <font>
       <sz val="10"/>
       <color rgb="FF333333"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="10"/>
-      <color rgb="FF777777"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -721,7 +717,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -748,9 +744,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1121,7 +1114,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H136"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1134,46 +1127,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="18"/>
-      <c r="C2" s="18"/>
-      <c r="D2" s="21" t="s">
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="18"/>
-      <c r="F2" s="19" t="s">
+      <c r="E2" s="17"/>
+      <c r="F2" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="18"/>
+      <c r="G2" s="17"/>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="20" t="s">
+      <c r="A3" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="18"/>
-      <c r="C3" s="18"/>
-      <c r="D3" s="18"/>
-      <c r="E3" s="18"/>
-      <c r="F3" s="18"/>
-      <c r="G3" s="18"/>
-      <c r="H3" s="18"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
     </row>
     <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
@@ -1202,22 +1195,22 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G5" s="11" t="s">
@@ -1228,22 +1221,22 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
-      <c r="B6" s="16" t="s">
+      <c r="B6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C6" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="14" t="s">
         <v>24</v>
       </c>
-      <c r="F6" s="15" t="s">
+      <c r="F6" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G6" s="11" t="s">
@@ -1254,22 +1247,22 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A7" s="15" t="s">
+      <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="15" t="s">
+      <c r="F7" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="11" t="s">
@@ -1280,22 +1273,22 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A8" s="15" t="s">
+      <c r="A8" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="C8" s="14" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="15" t="s">
+      <c r="F8" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G8" s="11" t="s">
@@ -1306,22 +1299,22 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="15" t="s">
+      <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="B9" s="16" t="s">
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="F9" s="15" t="s">
+      <c r="F9" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G9" s="11" t="s">
@@ -1332,22 +1325,22 @@
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" s="15" t="s">
+      <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B10" s="16" t="s">
+      <c r="B10" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="15" t="s">
+      <c r="C10" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="F10" s="15" t="s">
+      <c r="F10" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G10" s="11" t="s">
@@ -1358,22 +1351,22 @@
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A11" s="15" t="s">
+      <c r="A11" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G11" s="11" t="s">
@@ -1384,22 +1377,22 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B12" s="16" t="s">
+      <c r="B12" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="15" t="s">
+      <c r="C12" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G12" s="11" t="s">
@@ -1410,22 +1403,22 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="14" t="s">
         <v>51</v>
       </c>
-      <c r="B13" s="16" t="s">
+      <c r="B13" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C13" s="15" t="s">
+      <c r="C13" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G13" s="11" t="s">
@@ -1436,22 +1429,22 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="14" t="s">
         <v>56</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C14" s="15" t="s">
+      <c r="C14" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="11" t="s">
@@ -1462,44 +1455,44 @@
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A15" s="15" t="s">
+      <c r="A15" s="14" t="s">
         <v>58</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G15" s="11"/>
       <c r="H15" s="11"/>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B16" s="16" t="s">
+      <c r="B16" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C16" s="15" t="s">
+      <c r="C16" s="14" t="s">
         <v>53</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G16" s="11" t="s">
@@ -1509,23 +1502,23 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="15" t="s">
+    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="B17" s="16" t="s">
+      <c r="B17" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="C17" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="11" t="s">
@@ -1535,23 +1528,23 @@
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A18" s="15" t="s">
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="B18" s="16" t="s">
+      <c r="B18" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C18" s="15" t="s">
+      <c r="C18" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="14" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="11" t="s">
@@ -1561,1697 +1554,1700 @@
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A19" s="15" t="s">
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="14" t="s">
         <v>67</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="14" t="s">
         <v>63</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G19" s="12" t="s">
+      <c r="G19" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H19" s="12" t="s">
+      <c r="H19" s="11" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="15" t="s">
+    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A20" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="B20" s="16" t="s">
+      <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C20" s="15" t="s">
+      <c r="C20" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D20" s="15" t="s">
+      <c r="D20" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E20" s="15" t="s">
+      <c r="E20" s="14" t="s">
         <v>71</v>
       </c>
-      <c r="F20" s="15" t="s">
+      <c r="F20" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G20" s="12" t="s">
+      <c r="G20" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="H20" s="12" t="s">
+      <c r="H20" s="11" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="15" t="s">
+    <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="B21" s="16" t="s">
+      <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C21" s="15" t="s">
+      <c r="C21" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D21" s="15" t="s">
+      <c r="D21" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E21" s="15" t="s">
+      <c r="E21" s="14" t="s">
         <v>73</v>
       </c>
-      <c r="F21" s="15" t="s">
+      <c r="F21" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G21" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H21" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+      <c r="G21" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A22" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="B22" s="16" t="s">
+      <c r="B22" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C22" s="14" t="s">
         <v>70</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D22" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E22" s="15" t="s">
+      <c r="E22" s="14" t="s">
         <v>75</v>
       </c>
-      <c r="F22" s="15" t="s">
+      <c r="F22" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G22" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H22" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+      <c r="G22" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="K22" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="14" t="s">
         <v>76</v>
       </c>
-      <c r="B23" s="16" t="s">
+      <c r="B23" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D23" s="15" t="s">
+      <c r="D23" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E23" s="15" t="s">
+      <c r="E23" s="14" t="s">
         <v>79</v>
       </c>
-      <c r="F23" s="15" t="s">
+      <c r="F23" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G23" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H23" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
+      <c r="G23" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H23" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A24" s="14" t="s">
         <v>80</v>
       </c>
-      <c r="B24" s="16" t="s">
+      <c r="B24" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C24" s="15" t="s">
+      <c r="C24" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D24" s="15" t="s">
+      <c r="D24" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E24" s="15" t="s">
+      <c r="E24" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="F24" s="15" t="s">
+      <c r="F24" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G24" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H24" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A25" s="15" t="s">
+      <c r="G24" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="B25" s="16" t="s">
+      <c r="B25" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="C25" s="14" t="s">
         <v>78</v>
       </c>
-      <c r="D25" s="15" t="s">
+      <c r="D25" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E25" s="15" t="s">
+      <c r="E25" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="F25" s="15" t="s">
+      <c r="F25" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G25" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="G25" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H25" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C26" s="15" t="s">
+      <c r="C26" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D26" s="15" t="s">
+      <c r="D26" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E26" s="15" t="s">
+      <c r="E26" s="14" t="s">
         <v>86</v>
       </c>
-      <c r="F26" s="15" t="s">
+      <c r="F26" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G26" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H26" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A27" s="15" t="s">
+      <c r="G26" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H26" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="16" t="s">
+      <c r="B27" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C27" s="15" t="s">
+      <c r="C27" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D27" s="15" t="s">
+      <c r="D27" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E27" s="15" t="s">
+      <c r="E27" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="F27" s="15" t="s">
+      <c r="F27" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G27" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H27" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
+      <c r="G27" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="B28" s="16" t="s">
+      <c r="B28" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C28" s="15" t="s">
+      <c r="C28" s="14" t="s">
         <v>85</v>
       </c>
-      <c r="D28" s="15" t="s">
+      <c r="D28" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="E28" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="F28" s="15" t="s">
+      <c r="F28" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G28" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H28" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A29" s="15" t="s">
+      <c r="G28" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H28" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="A29" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="B29" s="16" t="s">
+      <c r="B29" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C29" s="15" t="s">
+      <c r="C29" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D29" s="15" t="s">
+      <c r="D29" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E29" s="15" t="s">
+      <c r="E29" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F29" s="15" t="s">
+      <c r="F29" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G29" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H29" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="15" t="s">
+      <c r="G29" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B30" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C30" s="15" t="s">
+      <c r="C30" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D30" s="15" t="s">
+      <c r="D30" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E30" s="15" t="s">
+      <c r="E30" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F30" s="15" t="s">
+      <c r="F30" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G30" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H30" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="15" t="s">
+      <c r="G30" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B31" s="16" t="s">
+      <c r="B31" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="C31" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="D31" s="15" t="s">
+      <c r="D31" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E31" s="15" t="s">
+      <c r="E31" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F31" s="15" t="s">
+      <c r="F31" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G31" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H31" s="14" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" s="15" t="s">
+      <c r="G31" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H31" s="13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="B32" s="16" t="s">
+      <c r="B32" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C32" s="15" t="s">
+      <c r="C32" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D32" s="15" t="s">
+      <c r="D32" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E32" s="15" t="s">
+      <c r="E32" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="15" t="s">
+      <c r="F32" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G32" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H32" s="14" t="s">
+      <c r="G32" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H32" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A33" s="15" t="s">
+      <c r="A33" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="B33" s="16" t="s">
+      <c r="B33" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C33" s="15" t="s">
+      <c r="C33" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D33" s="15" t="s">
+      <c r="D33" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E33" s="15" t="s">
+      <c r="E33" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="F33" s="15" t="s">
+      <c r="F33" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G33" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H33" s="14" t="s">
+      <c r="G33" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H33" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A34" s="15" t="s">
+      <c r="A34" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B34" s="16" t="s">
+      <c r="B34" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C34" s="15" t="s">
+      <c r="C34" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D34" s="15" t="s">
+      <c r="D34" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E34" s="15" t="s">
+      <c r="E34" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="F34" s="15" t="s">
+      <c r="F34" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G34" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H34" s="14" t="s">
+      <c r="G34" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H34" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="14" t="s">
         <v>106</v>
       </c>
-      <c r="B35" s="16" t="s">
+      <c r="B35" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C35" s="15" t="s">
+      <c r="C35" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D35" s="15" t="s">
+      <c r="D35" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E35" s="15" t="s">
+      <c r="E35" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="F35" s="15" t="s">
+      <c r="F35" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G35" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H35" s="14" t="s">
+      <c r="G35" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H35" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A36" s="15" t="s">
+      <c r="A36" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C36" s="15" t="s">
+      <c r="C36" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D36" s="15" t="s">
+      <c r="D36" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E36" s="15" t="s">
+      <c r="E36" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="F36" s="15" t="s">
+      <c r="F36" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G36" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H36" s="14" t="s">
+      <c r="G36" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H36" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C37" s="15" t="s">
+      <c r="C37" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D37" s="15" t="s">
+      <c r="D37" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E37" s="15" t="s">
+      <c r="E37" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="F37" s="15" t="s">
+      <c r="F37" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G37" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H37" s="14" t="s">
+      <c r="G37" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H37" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" s="15" t="s">
+      <c r="A38" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C38" s="15" t="s">
+      <c r="C38" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D38" s="15" t="s">
+      <c r="D38" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="15" t="s">
+      <c r="E38" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F38" s="15" t="s">
+      <c r="F38" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G38" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H38" s="14" t="s">
+      <c r="G38" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H38" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="B39" s="16" t="s">
+      <c r="B39" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="15" t="s">
+      <c r="C39" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D39" s="15" t="s">
+      <c r="D39" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E39" s="15" t="s">
+      <c r="E39" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="F39" s="15" t="s">
+      <c r="F39" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G39" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H39" s="14" t="s">
+      <c r="G39" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H39" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A40" s="15" t="s">
+      <c r="A40" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="B40" s="16" t="s">
+      <c r="B40" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C40" s="15" t="s">
+      <c r="C40" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D40" s="15" t="s">
+      <c r="D40" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E40" s="15" t="s">
+      <c r="E40" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F40" s="15" t="s">
+      <c r="F40" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H40" s="14" t="s">
+      <c r="G40" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H40" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A41" s="15" t="s">
+      <c r="A41" s="14" t="s">
         <v>120</v>
       </c>
-      <c r="B41" s="16" t="s">
+      <c r="B41" s="15" t="s">
         <v>99</v>
       </c>
-      <c r="C41" s="15" t="s">
+      <c r="C41" s="14" t="s">
         <v>116</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E41" s="15" t="s">
+      <c r="E41" s="14" t="s">
         <v>121</v>
       </c>
-      <c r="F41" s="15" t="s">
+      <c r="F41" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H41" s="14" t="s">
+      <c r="G41" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H41" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="15" t="s">
+      <c r="A42" s="14" t="s">
         <v>122</v>
       </c>
-      <c r="B42" s="16" t="s">
+      <c r="B42" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C42" s="15" t="s">
+      <c r="C42" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E42" s="15" t="s">
+      <c r="E42" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="F42" s="15" t="s">
+      <c r="F42" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G42" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H42" s="14" t="s">
+      <c r="G42" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H42" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A43" s="15" t="s">
+      <c r="A43" s="14" t="s">
         <v>126</v>
       </c>
-      <c r="B43" s="16" t="s">
+      <c r="B43" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C43" s="15" t="s">
+      <c r="C43" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E43" s="15" t="s">
+      <c r="E43" s="14" t="s">
         <v>127</v>
       </c>
-      <c r="F43" s="15" t="s">
+      <c r="F43" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G43" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H43" s="14" t="s">
+      <c r="G43" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H43" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" s="15" t="s">
+      <c r="A44" s="14" t="s">
         <v>128</v>
       </c>
-      <c r="B44" s="16" t="s">
+      <c r="B44" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C44" s="15" t="s">
+      <c r="C44" s="14" t="s">
         <v>124</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E44" s="15" t="s">
+      <c r="E44" s="14" t="s">
         <v>129</v>
       </c>
-      <c r="F44" s="15" t="s">
+      <c r="F44" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G44" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H44" s="14" t="s">
+      <c r="G44" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H44" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
+      <c r="A45" s="14" t="s">
         <v>130</v>
       </c>
-      <c r="B45" s="16" t="s">
+      <c r="B45" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C45" s="15" t="s">
+      <c r="C45" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E45" s="15" t="s">
+      <c r="E45" s="14" t="s">
         <v>132</v>
       </c>
-      <c r="F45" s="15" t="s">
+      <c r="F45" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G45" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H45" s="14" t="s">
+      <c r="G45" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
+      <c r="A46" s="14" t="s">
         <v>133</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B46" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C46" s="15" t="s">
+      <c r="C46" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E46" s="15" t="s">
+      <c r="E46" s="14" t="s">
         <v>134</v>
       </c>
-      <c r="F46" s="15" t="s">
+      <c r="F46" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G46" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H46" s="14" t="s">
+      <c r="G46" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H46" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="14" t="s">
         <v>135</v>
       </c>
-      <c r="B47" s="16" t="s">
+      <c r="B47" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C47" s="15" t="s">
+      <c r="C47" s="14" t="s">
         <v>131</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E47" s="15" t="s">
+      <c r="E47" s="14" t="s">
         <v>136</v>
       </c>
-      <c r="F47" s="15" t="s">
+      <c r="F47" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G47" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H47" s="14" t="s">
+      <c r="G47" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H47" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A48" s="15" t="s">
+      <c r="A48" s="14" t="s">
         <v>137</v>
       </c>
-      <c r="B48" s="16" t="s">
+      <c r="B48" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C48" s="15" t="s">
+      <c r="C48" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="E48" s="15" t="s">
+      <c r="E48" s="14" t="s">
         <v>139</v>
       </c>
-      <c r="F48" s="15" t="s">
+      <c r="F48" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="G48" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H48" s="14" t="s">
+      <c r="G48" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H48" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+      <c r="A49" s="14" t="s">
         <v>140</v>
       </c>
-      <c r="B49" s="16" t="s">
+      <c r="B49" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C49" s="15" t="s">
+      <c r="C49" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="14" t="s">
         <v>23</v>
       </c>
-      <c r="E49" s="15" t="s">
+      <c r="E49" s="14" t="s">
         <v>141</v>
       </c>
-      <c r="F49" s="15" t="s">
+      <c r="F49" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G49" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H49" s="14" t="s">
+      <c r="G49" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H49" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
-      <c r="A50" s="15" t="s">
+      <c r="A50" s="14" t="s">
         <v>142</v>
       </c>
-      <c r="B50" s="16" t="s">
+      <c r="B50" s="15" t="s">
         <v>123</v>
       </c>
-      <c r="C50" s="15" t="s">
+      <c r="C50" s="14" t="s">
         <v>138</v>
       </c>
-      <c r="D50" s="15" t="s">
+      <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E50" s="15" t="s">
+      <c r="E50" s="14" t="s">
         <v>143</v>
       </c>
-      <c r="F50" s="15" t="s">
+      <c r="F50" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G50" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="H50" s="14" t="s">
+      <c r="G50" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="H50" s="13" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A51" s="13"/>
-      <c r="B51" s="13"/>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="14"/>
-      <c r="H51" s="14"/>
+      <c r="A51" s="12"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="12"/>
+      <c r="D51" s="12"/>
+      <c r="E51" s="12"/>
+      <c r="F51" s="12"/>
+      <c r="G51" s="13"/>
+      <c r="H51" s="13"/>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A52" s="13"/>
-      <c r="B52" s="13"/>
-      <c r="C52" s="13"/>
-      <c r="D52" s="13"/>
-      <c r="E52" s="13"/>
-      <c r="F52" s="13"/>
-      <c r="G52" s="14"/>
-      <c r="H52" s="14"/>
+      <c r="A52" s="12"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="12"/>
+      <c r="D52" s="12"/>
+      <c r="E52" s="12"/>
+      <c r="F52" s="12"/>
+      <c r="G52" s="13"/>
+      <c r="H52" s="13"/>
     </row>
     <row r="53" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A53" s="13"/>
-      <c r="B53" s="13"/>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="14"/>
-      <c r="H53" s="14"/>
+      <c r="A53" s="12"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="12"/>
+      <c r="D53" s="12"/>
+      <c r="E53" s="12"/>
+      <c r="F53" s="12"/>
+      <c r="G53" s="13"/>
+      <c r="H53" s="13"/>
     </row>
     <row r="54" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A54" s="13"/>
-      <c r="B54" s="13"/>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="14"/>
-      <c r="H54" s="14"/>
+      <c r="A54" s="12"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="12"/>
+      <c r="D54" s="12"/>
+      <c r="E54" s="12"/>
+      <c r="F54" s="12"/>
+      <c r="G54" s="13"/>
+      <c r="H54" s="13"/>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="13"/>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="14"/>
-      <c r="H55" s="14"/>
+      <c r="A55" s="12"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="12"/>
+      <c r="D55" s="12"/>
+      <c r="E55" s="12"/>
+      <c r="F55" s="12"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="13"/>
-      <c r="B56" s="13"/>
-      <c r="C56" s="13"/>
-      <c r="D56" s="13"/>
-      <c r="E56" s="13"/>
-      <c r="F56" s="13"/>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14"/>
+      <c r="A56" s="12"/>
+      <c r="B56" s="12"/>
+      <c r="C56" s="12"/>
+      <c r="D56" s="12"/>
+      <c r="E56" s="12"/>
+      <c r="F56" s="12"/>
+      <c r="G56" s="13"/>
+      <c r="H56" s="13"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A57" s="13"/>
-      <c r="B57" s="13"/>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
-      <c r="G57" s="14"/>
-      <c r="H57" s="14"/>
+      <c r="A57" s="12"/>
+      <c r="B57" s="12"/>
+      <c r="C57" s="12"/>
+      <c r="D57" s="12"/>
+      <c r="E57" s="12"/>
+      <c r="F57" s="12"/>
+      <c r="G57" s="13"/>
+      <c r="H57" s="13"/>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A58" s="13"/>
-      <c r="B58" s="13"/>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14"/>
+      <c r="A58" s="12"/>
+      <c r="B58" s="12"/>
+      <c r="C58" s="12"/>
+      <c r="D58" s="12"/>
+      <c r="E58" s="12"/>
+      <c r="F58" s="12"/>
+      <c r="G58" s="13"/>
+      <c r="H58" s="13"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A59" s="13"/>
-      <c r="B59" s="13"/>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
-      <c r="G59" s="14"/>
-      <c r="H59" s="14"/>
+      <c r="A59" s="12"/>
+      <c r="B59" s="12"/>
+      <c r="C59" s="12"/>
+      <c r="D59" s="12"/>
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A60" s="13"/>
-      <c r="B60" s="13"/>
-      <c r="C60" s="13"/>
-      <c r="D60" s="13"/>
-      <c r="E60" s="13"/>
-      <c r="F60" s="13"/>
-      <c r="G60" s="14"/>
-      <c r="H60" s="14"/>
+      <c r="A60" s="12"/>
+      <c r="B60" s="12"/>
+      <c r="C60" s="12"/>
+      <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="13"/>
+      <c r="H60" s="13"/>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A61" s="13"/>
-      <c r="B61" s="13"/>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
-      <c r="G61" s="14"/>
-      <c r="H61" s="14"/>
+      <c r="A61" s="12"/>
+      <c r="B61" s="12"/>
+      <c r="C61" s="12"/>
+      <c r="D61" s="12"/>
+      <c r="E61" s="12"/>
+      <c r="F61" s="12"/>
+      <c r="G61" s="13"/>
+      <c r="H61" s="13"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A62" s="13"/>
-      <c r="B62" s="13"/>
-      <c r="C62" s="13"/>
-      <c r="D62" s="13"/>
-      <c r="E62" s="13"/>
-      <c r="F62" s="13"/>
-      <c r="G62" s="14"/>
-      <c r="H62" s="14"/>
+      <c r="A62" s="12"/>
+      <c r="B62" s="12"/>
+      <c r="C62" s="12"/>
+      <c r="D62" s="12"/>
+      <c r="E62" s="12"/>
+      <c r="F62" s="12"/>
+      <c r="G62" s="13"/>
+      <c r="H62" s="13"/>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A63" s="13"/>
-      <c r="B63" s="13"/>
-      <c r="C63" s="13"/>
-      <c r="D63" s="13"/>
-      <c r="E63" s="13"/>
-      <c r="F63" s="13"/>
-      <c r="G63" s="14"/>
-      <c r="H63" s="14"/>
+      <c r="A63" s="12"/>
+      <c r="B63" s="12"/>
+      <c r="C63" s="12"/>
+      <c r="D63" s="12"/>
+      <c r="E63" s="12"/>
+      <c r="F63" s="12"/>
+      <c r="G63" s="13"/>
+      <c r="H63" s="13"/>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A64" s="13"/>
-      <c r="B64" s="13"/>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
-      <c r="G64" s="14"/>
-      <c r="H64" s="14"/>
+      <c r="A64" s="12"/>
+      <c r="B64" s="12"/>
+      <c r="C64" s="12"/>
+      <c r="D64" s="12"/>
+      <c r="E64" s="12"/>
+      <c r="F64" s="12"/>
+      <c r="G64" s="13"/>
+      <c r="H64" s="13"/>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="13"/>
-      <c r="B65" s="13"/>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
-      <c r="G65" s="14"/>
-      <c r="H65" s="14"/>
+      <c r="A65" s="12"/>
+      <c r="B65" s="12"/>
+      <c r="C65" s="12"/>
+      <c r="D65" s="12"/>
+      <c r="E65" s="12"/>
+      <c r="F65" s="12"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A66" s="13"/>
-      <c r="B66" s="13"/>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
-      <c r="G66" s="14"/>
-      <c r="H66" s="14"/>
+      <c r="A66" s="12"/>
+      <c r="B66" s="12"/>
+      <c r="C66" s="12"/>
+      <c r="D66" s="12"/>
+      <c r="E66" s="12"/>
+      <c r="F66" s="12"/>
+      <c r="G66" s="13"/>
+      <c r="H66" s="13"/>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A67" s="13"/>
-      <c r="B67" s="13"/>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
-      <c r="G67" s="14"/>
-      <c r="H67" s="14"/>
+      <c r="A67" s="12"/>
+      <c r="B67" s="12"/>
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12"/>
+      <c r="G67" s="13"/>
+      <c r="H67" s="13"/>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68" s="13"/>
-      <c r="B68" s="13"/>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
-      <c r="G68" s="14"/>
-      <c r="H68" s="14"/>
+      <c r="A68" s="12"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="12"/>
+      <c r="E68" s="12"/>
+      <c r="F68" s="12"/>
+      <c r="G68" s="13"/>
+      <c r="H68" s="13"/>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A69" s="13"/>
-      <c r="B69" s="13"/>
-      <c r="C69" s="13"/>
-      <c r="D69" s="13"/>
-      <c r="E69" s="13"/>
-      <c r="F69" s="13"/>
-      <c r="G69" s="14"/>
-      <c r="H69" s="14"/>
+      <c r="A69" s="12"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="12"/>
+      <c r="D69" s="12"/>
+      <c r="E69" s="12"/>
+      <c r="F69" s="12"/>
+      <c r="G69" s="13"/>
+      <c r="H69" s="13"/>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A70" s="13"/>
-      <c r="B70" s="13"/>
-      <c r="C70" s="13"/>
-      <c r="D70" s="13"/>
-      <c r="E70" s="13"/>
-      <c r="F70" s="13"/>
-      <c r="G70" s="14"/>
-      <c r="H70" s="14"/>
+      <c r="A70" s="12"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="12"/>
+      <c r="G70" s="13"/>
+      <c r="H70" s="13"/>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A71" s="13"/>
-      <c r="B71" s="13"/>
-      <c r="C71" s="13"/>
-      <c r="D71" s="13"/>
-      <c r="E71" s="13"/>
-      <c r="F71" s="13"/>
-      <c r="G71" s="14"/>
-      <c r="H71" s="14"/>
+      <c r="A71" s="12"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="12"/>
+      <c r="G71" s="13"/>
+      <c r="H71" s="13"/>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A72" s="13"/>
-      <c r="B72" s="13"/>
-      <c r="C72" s="13"/>
-      <c r="D72" s="13"/>
-      <c r="E72" s="13"/>
-      <c r="F72" s="13"/>
-      <c r="G72" s="14"/>
-      <c r="H72" s="14"/>
+      <c r="A72" s="12"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="12"/>
+      <c r="G72" s="13"/>
+      <c r="H72" s="13"/>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A73" s="13"/>
-      <c r="B73" s="13"/>
-      <c r="C73" s="13"/>
-      <c r="D73" s="13"/>
-      <c r="E73" s="13"/>
-      <c r="F73" s="13"/>
-      <c r="G73" s="14"/>
-      <c r="H73" s="14"/>
+      <c r="A73" s="12"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="12"/>
+      <c r="D73" s="12"/>
+      <c r="E73" s="12"/>
+      <c r="F73" s="12"/>
+      <c r="G73" s="13"/>
+      <c r="H73" s="13"/>
     </row>
     <row r="74" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A74" s="13"/>
-      <c r="B74" s="13"/>
-      <c r="C74" s="13"/>
-      <c r="D74" s="13"/>
-      <c r="E74" s="13"/>
-      <c r="F74" s="13"/>
-      <c r="G74" s="14"/>
-      <c r="H74" s="14"/>
+      <c r="A74" s="12"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="12"/>
+      <c r="D74" s="12"/>
+      <c r="E74" s="12"/>
+      <c r="F74" s="12"/>
+      <c r="G74" s="13"/>
+      <c r="H74" s="13"/>
     </row>
     <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="13"/>
-      <c r="B75" s="13"/>
-      <c r="C75" s="13"/>
-      <c r="D75" s="13"/>
-      <c r="E75" s="13"/>
-      <c r="F75" s="13"/>
-      <c r="G75" s="14"/>
-      <c r="H75" s="14"/>
+      <c r="A75" s="12"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="12"/>
+      <c r="E75" s="12"/>
+      <c r="F75" s="12"/>
+      <c r="G75" s="13"/>
+      <c r="H75" s="13"/>
     </row>
     <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="13"/>
-      <c r="B76" s="13"/>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
-      <c r="G76" s="14"/>
-      <c r="H76" s="14"/>
+      <c r="A76" s="12"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="12"/>
+      <c r="D76" s="12"/>
+      <c r="E76" s="12"/>
+      <c r="F76" s="12"/>
+      <c r="G76" s="13"/>
+      <c r="H76" s="13"/>
     </row>
     <row r="77" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A77" s="13"/>
-      <c r="B77" s="13"/>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
-      <c r="G77" s="14"/>
-      <c r="H77" s="14"/>
+      <c r="A77" s="12"/>
+      <c r="B77" s="12"/>
+      <c r="C77" s="12"/>
+      <c r="D77" s="12"/>
+      <c r="E77" s="12"/>
+      <c r="F77" s="12"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A78" s="13"/>
-      <c r="B78" s="13"/>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
-      <c r="G78" s="14"/>
-      <c r="H78" s="14"/>
+      <c r="A78" s="12"/>
+      <c r="B78" s="12"/>
+      <c r="C78" s="12"/>
+      <c r="D78" s="12"/>
+      <c r="E78" s="12"/>
+      <c r="F78" s="12"/>
+      <c r="G78" s="13"/>
+      <c r="H78" s="13"/>
     </row>
     <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="13"/>
-      <c r="B79" s="13"/>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
-      <c r="G79" s="14"/>
-      <c r="H79" s="14"/>
+      <c r="A79" s="12"/>
+      <c r="B79" s="12"/>
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12"/>
+      <c r="G79" s="13"/>
+      <c r="H79" s="13"/>
     </row>
     <row r="80" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A80" s="13"/>
-      <c r="B80" s="13"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
+      <c r="A80" s="12"/>
+      <c r="B80" s="12"/>
+      <c r="C80" s="12"/>
+      <c r="D80" s="12"/>
+      <c r="E80" s="12"/>
+      <c r="F80" s="12"/>
+      <c r="G80" s="13"/>
+      <c r="H80" s="13"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A81" s="13"/>
-      <c r="B81" s="13"/>
-      <c r="C81" s="13"/>
-      <c r="D81" s="13"/>
-      <c r="E81" s="13"/>
-      <c r="F81" s="13"/>
-      <c r="G81" s="14"/>
-      <c r="H81" s="14"/>
+      <c r="A81" s="12"/>
+      <c r="B81" s="12"/>
+      <c r="C81" s="12"/>
+      <c r="D81" s="12"/>
+      <c r="E81" s="12"/>
+      <c r="F81" s="12"/>
+      <c r="G81" s="13"/>
+      <c r="H81" s="13"/>
     </row>
     <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="13"/>
-      <c r="B82" s="13"/>
-      <c r="C82" s="13"/>
-      <c r="D82" s="13"/>
-      <c r="E82" s="13"/>
-      <c r="F82" s="13"/>
-      <c r="G82" s="14"/>
-      <c r="H82" s="14"/>
+      <c r="A82" s="12"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="12"/>
+      <c r="G82" s="13"/>
+      <c r="H82" s="13"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A83" s="13"/>
-      <c r="B83" s="13"/>
-      <c r="C83" s="13"/>
-      <c r="D83" s="13"/>
-      <c r="E83" s="13"/>
-      <c r="F83" s="13"/>
-      <c r="G83" s="14"/>
-      <c r="H83" s="14"/>
+      <c r="A83" s="12"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="12"/>
+      <c r="G83" s="13"/>
+      <c r="H83" s="13"/>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A84" s="13"/>
-      <c r="B84" s="13"/>
-      <c r="C84" s="13"/>
-      <c r="D84" s="13"/>
-      <c r="E84" s="13"/>
-      <c r="F84" s="13"/>
-      <c r="G84" s="14"/>
-      <c r="H84" s="14"/>
+      <c r="A84" s="12"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="12"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A85" s="13"/>
-      <c r="B85" s="13"/>
-      <c r="C85" s="13"/>
-      <c r="D85" s="13"/>
-      <c r="E85" s="13"/>
-      <c r="F85" s="13"/>
-      <c r="G85" s="14"/>
-      <c r="H85" s="14"/>
+      <c r="A85" s="12"/>
+      <c r="B85" s="12"/>
+      <c r="C85" s="12"/>
+      <c r="D85" s="12"/>
+      <c r="E85" s="12"/>
+      <c r="F85" s="12"/>
+      <c r="G85" s="13"/>
+      <c r="H85" s="13"/>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A86" s="13"/>
-      <c r="B86" s="13"/>
-      <c r="C86" s="13"/>
-      <c r="D86" s="13"/>
-      <c r="E86" s="13"/>
-      <c r="F86" s="13"/>
-      <c r="G86" s="14"/>
-      <c r="H86" s="14"/>
+      <c r="A86" s="12"/>
+      <c r="B86" s="12"/>
+      <c r="C86" s="12"/>
+      <c r="D86" s="12"/>
+      <c r="E86" s="12"/>
+      <c r="F86" s="12"/>
+      <c r="G86" s="13"/>
+      <c r="H86" s="13"/>
     </row>
     <row r="87" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A87" s="13"/>
-      <c r="B87" s="13"/>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
-      <c r="G87" s="14"/>
-      <c r="H87" s="14"/>
+      <c r="A87" s="12"/>
+      <c r="B87" s="12"/>
+      <c r="C87" s="12"/>
+      <c r="D87" s="12"/>
+      <c r="E87" s="12"/>
+      <c r="F87" s="12"/>
+      <c r="G87" s="13"/>
+      <c r="H87" s="13"/>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A88" s="13"/>
-      <c r="B88" s="13"/>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
-      <c r="G88" s="14"/>
-      <c r="H88" s="14"/>
+      <c r="A88" s="12"/>
+      <c r="B88" s="12"/>
+      <c r="C88" s="12"/>
+      <c r="D88" s="12"/>
+      <c r="E88" s="12"/>
+      <c r="F88" s="12"/>
+      <c r="G88" s="13"/>
+      <c r="H88" s="13"/>
     </row>
     <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="13"/>
-      <c r="B89" s="13"/>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
-      <c r="G89" s="14"/>
-      <c r="H89" s="14"/>
+      <c r="A89" s="12"/>
+      <c r="B89" s="12"/>
+      <c r="C89" s="12"/>
+      <c r="D89" s="12"/>
+      <c r="E89" s="12"/>
+      <c r="F89" s="12"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
     </row>
     <row r="90" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A90" s="13"/>
-      <c r="B90" s="13"/>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
-      <c r="G90" s="14"/>
-      <c r="H90" s="14"/>
+      <c r="A90" s="12"/>
+      <c r="B90" s="12"/>
+      <c r="C90" s="12"/>
+      <c r="D90" s="12"/>
+      <c r="E90" s="12"/>
+      <c r="F90" s="12"/>
+      <c r="G90" s="13"/>
+      <c r="H90" s="13"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A91" s="13"/>
-      <c r="B91" s="13"/>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
-      <c r="G91" s="14"/>
-      <c r="H91" s="14"/>
+      <c r="A91" s="12"/>
+      <c r="B91" s="12"/>
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12"/>
+      <c r="G91" s="13"/>
+      <c r="H91" s="13"/>
     </row>
     <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="13"/>
-      <c r="B92" s="13"/>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
-      <c r="G92" s="14"/>
-      <c r="H92" s="14"/>
+      <c r="A92" s="12"/>
+      <c r="B92" s="12"/>
+      <c r="C92" s="12"/>
+      <c r="D92" s="12"/>
+      <c r="E92" s="12"/>
+      <c r="F92" s="12"/>
+      <c r="G92" s="13"/>
+      <c r="H92" s="13"/>
     </row>
     <row r="93" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A93" s="13"/>
-      <c r="B93" s="13"/>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
-      <c r="G93" s="14"/>
-      <c r="H93" s="14"/>
+      <c r="A93" s="12"/>
+      <c r="B93" s="12"/>
+      <c r="C93" s="12"/>
+      <c r="D93" s="12"/>
+      <c r="E93" s="12"/>
+      <c r="F93" s="12"/>
+      <c r="G93" s="13"/>
+      <c r="H93" s="13"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A94" s="13"/>
-      <c r="B94" s="13"/>
-      <c r="C94" s="13"/>
-      <c r="D94" s="13"/>
-      <c r="E94" s="13"/>
-      <c r="F94" s="13"/>
-      <c r="G94" s="14"/>
-      <c r="H94" s="14"/>
+      <c r="A94" s="12"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="12"/>
+      <c r="G94" s="13"/>
+      <c r="H94" s="13"/>
     </row>
     <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="13"/>
-      <c r="B95" s="13"/>
-      <c r="C95" s="13"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
-      <c r="G95" s="14"/>
-      <c r="H95" s="14"/>
+      <c r="A95" s="12"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="12"/>
+      <c r="G95" s="13"/>
+      <c r="H95" s="13"/>
     </row>
     <row r="96" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A96" s="13"/>
-      <c r="B96" s="13"/>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
-      <c r="G96" s="14"/>
-      <c r="H96" s="14"/>
+      <c r="A96" s="12"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="12"/>
+      <c r="G96" s="13"/>
+      <c r="H96" s="13"/>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A97" s="13"/>
-      <c r="B97" s="13"/>
-      <c r="C97" s="13"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
-      <c r="G97" s="14"/>
-      <c r="H97" s="14"/>
+      <c r="A97" s="12"/>
+      <c r="B97" s="12"/>
+      <c r="C97" s="12"/>
+      <c r="D97" s="12"/>
+      <c r="E97" s="12"/>
+      <c r="F97" s="12"/>
+      <c r="G97" s="13"/>
+      <c r="H97" s="13"/>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="13"/>
-      <c r="B98" s="13"/>
-      <c r="C98" s="13"/>
-      <c r="D98" s="13"/>
-      <c r="E98" s="13"/>
-      <c r="F98" s="13"/>
-      <c r="G98" s="14"/>
-      <c r="H98" s="14"/>
+      <c r="A98" s="12"/>
+      <c r="B98" s="12"/>
+      <c r="C98" s="12"/>
+      <c r="D98" s="12"/>
+      <c r="E98" s="12"/>
+      <c r="F98" s="12"/>
+      <c r="G98" s="13"/>
+      <c r="H98" s="13"/>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="13"/>
-      <c r="B99" s="13"/>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
-      <c r="G99" s="14"/>
-      <c r="H99" s="14"/>
+      <c r="A99" s="12"/>
+      <c r="B99" s="12"/>
+      <c r="C99" s="12"/>
+      <c r="D99" s="12"/>
+      <c r="E99" s="12"/>
+      <c r="F99" s="12"/>
+      <c r="G99" s="13"/>
+      <c r="H99" s="13"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A100" s="13"/>
-      <c r="B100" s="13"/>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
-      <c r="G100" s="14"/>
-      <c r="H100" s="14"/>
+      <c r="A100" s="12"/>
+      <c r="B100" s="12"/>
+      <c r="C100" s="12"/>
+      <c r="D100" s="12"/>
+      <c r="E100" s="12"/>
+      <c r="F100" s="12"/>
+      <c r="G100" s="13"/>
+      <c r="H100" s="13"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A101" s="13"/>
-      <c r="B101" s="13"/>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
-      <c r="G101" s="14"/>
-      <c r="H101" s="14"/>
+      <c r="A101" s="12"/>
+      <c r="B101" s="12"/>
+      <c r="C101" s="12"/>
+      <c r="D101" s="12"/>
+      <c r="E101" s="12"/>
+      <c r="F101" s="12"/>
+      <c r="G101" s="13"/>
+      <c r="H101" s="13"/>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A102" s="13"/>
-      <c r="B102" s="13"/>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
-      <c r="G102" s="14"/>
-      <c r="H102" s="14"/>
+      <c r="A102" s="12"/>
+      <c r="B102" s="12"/>
+      <c r="C102" s="12"/>
+      <c r="D102" s="12"/>
+      <c r="E102" s="12"/>
+      <c r="F102" s="12"/>
+      <c r="G102" s="13"/>
+      <c r="H102" s="13"/>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A103" s="13"/>
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
-      <c r="G103" s="14"/>
-      <c r="H103" s="14"/>
+      <c r="A103" s="12"/>
+      <c r="B103" s="12"/>
+      <c r="C103" s="12"/>
+      <c r="D103" s="12"/>
+      <c r="E103" s="12"/>
+      <c r="F103" s="12"/>
+      <c r="G103" s="13"/>
+      <c r="H103" s="13"/>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A104" s="13"/>
-      <c r="B104" s="13"/>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
-      <c r="G104" s="14"/>
-      <c r="H104" s="14"/>
+      <c r="A104" s="12"/>
+      <c r="B104" s="12"/>
+      <c r="C104" s="12"/>
+      <c r="D104" s="12"/>
+      <c r="E104" s="12"/>
+      <c r="F104" s="12"/>
+      <c r="G104" s="13"/>
+      <c r="H104" s="13"/>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A105" s="13"/>
-      <c r="B105" s="13"/>
-      <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
-      <c r="G105" s="14"/>
-      <c r="H105" s="14"/>
+      <c r="A105" s="12"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="12"/>
+      <c r="D105" s="12"/>
+      <c r="E105" s="12"/>
+      <c r="F105" s="12"/>
+      <c r="G105" s="13"/>
+      <c r="H105" s="13"/>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A106" s="13"/>
-      <c r="B106" s="13"/>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
-      <c r="G106" s="14"/>
-      <c r="H106" s="14"/>
+      <c r="A106" s="12"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="12"/>
+      <c r="E106" s="12"/>
+      <c r="F106" s="12"/>
+      <c r="G106" s="13"/>
+      <c r="H106" s="13"/>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A107" s="13"/>
-      <c r="B107" s="13"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
-      <c r="G107" s="14"/>
-      <c r="H107" s="14"/>
+      <c r="A107" s="12"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="12"/>
+      <c r="E107" s="12"/>
+      <c r="F107" s="12"/>
+      <c r="G107" s="13"/>
+      <c r="H107" s="13"/>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A108" s="13"/>
-      <c r="B108" s="13"/>
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
-      <c r="G108" s="14"/>
-      <c r="H108" s="14"/>
+      <c r="A108" s="12"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="12"/>
+      <c r="E108" s="12"/>
+      <c r="F108" s="12"/>
+      <c r="G108" s="13"/>
+      <c r="H108" s="13"/>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A109" s="13"/>
-      <c r="B109" s="13"/>
-      <c r="C109" s="13"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
-      <c r="G109" s="14"/>
-      <c r="H109" s="14"/>
+      <c r="A109" s="12"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="12"/>
+      <c r="E109" s="12"/>
+      <c r="F109" s="12"/>
+      <c r="G109" s="13"/>
+      <c r="H109" s="13"/>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="13"/>
-      <c r="B110" s="13"/>
-      <c r="C110" s="13"/>
-      <c r="D110" s="13"/>
-      <c r="E110" s="13"/>
-      <c r="F110" s="13"/>
-      <c r="G110" s="14"/>
-      <c r="H110" s="14"/>
+      <c r="A110" s="12"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="12"/>
+      <c r="E110" s="12"/>
+      <c r="F110" s="12"/>
+      <c r="G110" s="13"/>
+      <c r="H110" s="13"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A111" s="13"/>
-      <c r="B111" s="13"/>
-      <c r="C111" s="13"/>
-      <c r="D111" s="13"/>
-      <c r="E111" s="13"/>
-      <c r="F111" s="13"/>
-      <c r="G111" s="14"/>
-      <c r="H111" s="14"/>
+      <c r="A111" s="12"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="12"/>
+      <c r="E111" s="12"/>
+      <c r="F111" s="12"/>
+      <c r="G111" s="13"/>
+      <c r="H111" s="13"/>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A112" s="13"/>
-      <c r="B112" s="13"/>
-      <c r="C112" s="13"/>
-      <c r="D112" s="13"/>
-      <c r="E112" s="13"/>
-      <c r="F112" s="13"/>
-      <c r="G112" s="14"/>
-      <c r="H112" s="14"/>
+      <c r="A112" s="12"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="12"/>
+      <c r="E112" s="12"/>
+      <c r="F112" s="12"/>
+      <c r="G112" s="13"/>
+      <c r="H112" s="13"/>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A113" s="13"/>
-      <c r="B113" s="13"/>
-      <c r="C113" s="13"/>
-      <c r="D113" s="13"/>
-      <c r="E113" s="13"/>
-      <c r="F113" s="13"/>
-      <c r="G113" s="14"/>
-      <c r="H113" s="14"/>
+      <c r="A113" s="12"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="12"/>
+      <c r="E113" s="12"/>
+      <c r="F113" s="12"/>
+      <c r="G113" s="13"/>
+      <c r="H113" s="13"/>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A114" s="13"/>
-      <c r="B114" s="13"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="13"/>
-      <c r="F114" s="13"/>
-      <c r="G114" s="14"/>
-      <c r="H114" s="14"/>
+      <c r="A114" s="12"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="12"/>
+      <c r="E114" s="12"/>
+      <c r="F114" s="12"/>
+      <c r="G114" s="13"/>
+      <c r="H114" s="13"/>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A115" s="13"/>
-      <c r="B115" s="13"/>
-      <c r="C115" s="13"/>
-      <c r="D115" s="13"/>
-      <c r="E115" s="13"/>
-      <c r="F115" s="13"/>
-      <c r="G115" s="14"/>
-      <c r="H115" s="14"/>
+      <c r="A115" s="12"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="12"/>
+      <c r="E115" s="12"/>
+      <c r="F115" s="12"/>
+      <c r="G115" s="13"/>
+      <c r="H115" s="13"/>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A116" s="13"/>
-      <c r="B116" s="13"/>
-      <c r="C116" s="13"/>
-      <c r="D116" s="13"/>
-      <c r="E116" s="13"/>
-      <c r="F116" s="13"/>
-      <c r="G116" s="14"/>
-      <c r="H116" s="14"/>
+      <c r="A116" s="12"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="12"/>
+      <c r="E116" s="12"/>
+      <c r="F116" s="12"/>
+      <c r="G116" s="13"/>
+      <c r="H116" s="13"/>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A117" s="13"/>
-      <c r="B117" s="13"/>
-      <c r="C117" s="13"/>
-      <c r="D117" s="13"/>
-      <c r="E117" s="13"/>
-      <c r="F117" s="13"/>
-      <c r="G117" s="14"/>
-      <c r="H117" s="14"/>
+      <c r="A117" s="12"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="12"/>
+      <c r="E117" s="12"/>
+      <c r="F117" s="12"/>
+      <c r="G117" s="13"/>
+      <c r="H117" s="13"/>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A118" s="13"/>
-      <c r="B118" s="13"/>
-      <c r="C118" s="13"/>
-      <c r="D118" s="13"/>
-      <c r="E118" s="13"/>
-      <c r="F118" s="13"/>
-      <c r="G118" s="14"/>
-      <c r="H118" s="14"/>
+      <c r="A118" s="12"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="12"/>
+      <c r="E118" s="12"/>
+      <c r="F118" s="12"/>
+      <c r="G118" s="13"/>
+      <c r="H118" s="13"/>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A119" s="13"/>
-      <c r="B119" s="13"/>
-      <c r="C119" s="13"/>
-      <c r="D119" s="13"/>
-      <c r="E119" s="13"/>
-      <c r="F119" s="13"/>
-      <c r="G119" s="14"/>
-      <c r="H119" s="14"/>
+      <c r="A119" s="12"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="12"/>
+      <c r="E119" s="12"/>
+      <c r="F119" s="12"/>
+      <c r="G119" s="13"/>
+      <c r="H119" s="13"/>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A120" s="13"/>
-      <c r="B120" s="13"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
-      <c r="G120" s="14"/>
-      <c r="H120" s="14"/>
+      <c r="A120" s="12"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="12"/>
+      <c r="E120" s="12"/>
+      <c r="F120" s="12"/>
+      <c r="G120" s="13"/>
+      <c r="H120" s="13"/>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="13"/>
-      <c r="B121" s="13"/>
-      <c r="C121" s="13"/>
-      <c r="D121" s="13"/>
-      <c r="E121" s="13"/>
-      <c r="F121" s="13"/>
-      <c r="G121" s="14"/>
-      <c r="H121" s="14"/>
+      <c r="A121" s="12"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="12"/>
+      <c r="E121" s="12"/>
+      <c r="F121" s="12"/>
+      <c r="G121" s="13"/>
+      <c r="H121" s="13"/>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="13"/>
-      <c r="B122" s="13"/>
-      <c r="C122" s="13"/>
-      <c r="D122" s="13"/>
-      <c r="E122" s="13"/>
-      <c r="F122" s="13"/>
-      <c r="G122" s="14"/>
-      <c r="H122" s="14"/>
+      <c r="A122" s="12"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="12"/>
+      <c r="E122" s="12"/>
+      <c r="F122" s="12"/>
+      <c r="G122" s="13"/>
+      <c r="H122" s="13"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A123" s="13"/>
-      <c r="B123" s="13"/>
-      <c r="C123" s="13"/>
-      <c r="D123" s="13"/>
-      <c r="E123" s="13"/>
-      <c r="F123" s="13"/>
-      <c r="G123" s="14"/>
-      <c r="H123" s="14"/>
+      <c r="A123" s="12"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="12"/>
+      <c r="E123" s="12"/>
+      <c r="F123" s="12"/>
+      <c r="G123" s="13"/>
+      <c r="H123" s="13"/>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A124" s="13"/>
-      <c r="B124" s="13"/>
-      <c r="C124" s="13"/>
-      <c r="D124" s="13"/>
-      <c r="E124" s="13"/>
-      <c r="F124" s="13"/>
-      <c r="G124" s="14"/>
-      <c r="H124" s="14"/>
+      <c r="A124" s="12"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="12"/>
+      <c r="D124" s="12"/>
+      <c r="E124" s="12"/>
+      <c r="F124" s="12"/>
+      <c r="G124" s="13"/>
+      <c r="H124" s="13"/>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A125" s="13"/>
-      <c r="B125" s="13"/>
-      <c r="C125" s="13"/>
-      <c r="D125" s="13"/>
-      <c r="E125" s="13"/>
-      <c r="F125" s="13"/>
-      <c r="G125" s="14"/>
-      <c r="H125" s="14"/>
+      <c r="A125" s="12"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="12"/>
+      <c r="D125" s="12"/>
+      <c r="E125" s="12"/>
+      <c r="F125" s="12"/>
+      <c r="G125" s="13"/>
+      <c r="H125" s="13"/>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A126" s="13"/>
-      <c r="B126" s="13"/>
-      <c r="C126" s="13"/>
-      <c r="D126" s="13"/>
-      <c r="E126" s="13"/>
-      <c r="F126" s="13"/>
-      <c r="G126" s="14"/>
-      <c r="H126" s="14"/>
+      <c r="A126" s="12"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="12"/>
+      <c r="D126" s="12"/>
+      <c r="E126" s="12"/>
+      <c r="F126" s="12"/>
+      <c r="G126" s="13"/>
+      <c r="H126" s="13"/>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A127" s="13"/>
-      <c r="B127" s="13"/>
-      <c r="C127" s="13"/>
-      <c r="D127" s="13"/>
-      <c r="E127" s="13"/>
-      <c r="F127" s="13"/>
-      <c r="G127" s="14"/>
-      <c r="H127" s="14"/>
+      <c r="A127" s="12"/>
+      <c r="B127" s="12"/>
+      <c r="C127" s="12"/>
+      <c r="D127" s="12"/>
+      <c r="E127" s="12"/>
+      <c r="F127" s="12"/>
+      <c r="G127" s="13"/>
+      <c r="H127" s="13"/>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A128" s="13"/>
-      <c r="B128" s="13"/>
-      <c r="C128" s="13"/>
-      <c r="D128" s="13"/>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13"/>
-      <c r="G128" s="14"/>
-      <c r="H128" s="14"/>
+      <c r="A128" s="12"/>
+      <c r="B128" s="12"/>
+      <c r="C128" s="12"/>
+      <c r="D128" s="12"/>
+      <c r="E128" s="12"/>
+      <c r="F128" s="12"/>
+      <c r="G128" s="13"/>
+      <c r="H128" s="13"/>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="13"/>
-      <c r="B129" s="13"/>
-      <c r="C129" s="13"/>
-      <c r="D129" s="13"/>
-      <c r="E129" s="13"/>
-      <c r="F129" s="13"/>
-      <c r="G129" s="14"/>
-      <c r="H129" s="14"/>
+      <c r="A129" s="12"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="12"/>
+      <c r="D129" s="12"/>
+      <c r="E129" s="12"/>
+      <c r="F129" s="12"/>
+      <c r="G129" s="13"/>
+      <c r="H129" s="13"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A130" s="13"/>
-      <c r="B130" s="13"/>
-      <c r="C130" s="13"/>
-      <c r="D130" s="13"/>
-      <c r="E130" s="13"/>
-      <c r="F130" s="13"/>
-      <c r="G130" s="14"/>
-      <c r="H130" s="14"/>
+      <c r="A130" s="12"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="12"/>
+      <c r="D130" s="12"/>
+      <c r="E130" s="12"/>
+      <c r="F130" s="12"/>
+      <c r="G130" s="13"/>
+      <c r="H130" s="13"/>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A131" s="13"/>
-      <c r="B131" s="13"/>
-      <c r="C131" s="13"/>
-      <c r="D131" s="13"/>
-      <c r="E131" s="13"/>
-      <c r="F131" s="13"/>
-      <c r="G131" s="14"/>
-      <c r="H131" s="14"/>
+      <c r="A131" s="12"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="12"/>
+      <c r="D131" s="12"/>
+      <c r="E131" s="12"/>
+      <c r="F131" s="12"/>
+      <c r="G131" s="13"/>
+      <c r="H131" s="13"/>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A132" s="13"/>
-      <c r="B132" s="13"/>
-      <c r="C132" s="13"/>
-      <c r="D132" s="13"/>
-      <c r="E132" s="13"/>
-      <c r="F132" s="13"/>
-      <c r="G132" s="14"/>
-      <c r="H132" s="14"/>
+      <c r="A132" s="12"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="12"/>
+      <c r="D132" s="12"/>
+      <c r="E132" s="12"/>
+      <c r="F132" s="12"/>
+      <c r="G132" s="13"/>
+      <c r="H132" s="13"/>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A133" s="13"/>
-      <c r="B133" s="13"/>
-      <c r="C133" s="13"/>
-      <c r="D133" s="13"/>
-      <c r="E133" s="13"/>
-      <c r="F133" s="13"/>
-      <c r="G133" s="14"/>
-      <c r="H133" s="14"/>
+      <c r="A133" s="12"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="12"/>
+      <c r="D133" s="12"/>
+      <c r="E133" s="12"/>
+      <c r="F133" s="12"/>
+      <c r="G133" s="13"/>
+      <c r="H133" s="13"/>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A134" s="13"/>
-      <c r="B134" s="13"/>
-      <c r="C134" s="13"/>
-      <c r="D134" s="13"/>
-      <c r="E134" s="13"/>
-      <c r="F134" s="13"/>
-      <c r="G134" s="14"/>
-      <c r="H134" s="14"/>
+      <c r="A134" s="12"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="12"/>
+      <c r="D134" s="12"/>
+      <c r="E134" s="12"/>
+      <c r="F134" s="12"/>
+      <c r="G134" s="13"/>
+      <c r="H134" s="13"/>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A135" s="13"/>
-      <c r="B135" s="13"/>
-      <c r="C135" s="13"/>
-      <c r="D135" s="13"/>
-      <c r="E135" s="13"/>
-      <c r="F135" s="13"/>
-      <c r="G135" s="14"/>
-      <c r="H135" s="14"/>
+      <c r="A135" s="12"/>
+      <c r="B135" s="12"/>
+      <c r="C135" s="12"/>
+      <c r="D135" s="12"/>
+      <c r="E135" s="12"/>
+      <c r="F135" s="12"/>
+      <c r="G135" s="13"/>
+      <c r="H135" s="13"/>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="13"/>
-      <c r="B136" s="13"/>
-      <c r="C136" s="13"/>
-      <c r="D136" s="13"/>
-      <c r="E136" s="13"/>
-      <c r="F136" s="13"/>
-      <c r="G136" s="14"/>
-      <c r="H136" s="14"/>
+      <c r="A136" s="12"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="12"/>
+      <c r="D136" s="12"/>
+      <c r="E136" s="12"/>
+      <c r="F136" s="12"/>
+      <c r="G136" s="13"/>
+      <c r="H136" s="13"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H50" xr:uid="{00000000-0009-0000-0000-000000000000}">
@@ -3266,7 +3262,7 @@
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="D2:E2"/>
   </mergeCells>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <conditionalFormatting sqref="A5:H50">
     <cfRule type="expression" dxfId="2" priority="5">
       <formula>$B5="Onda 2"</formula>
@@ -3311,10 +3307,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B1" s="18"/>
+      <c r="B1" s="17"/>
     </row>
     <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
@@ -3389,106 +3385,106 @@
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="24" t="s">
+      <c r="A12" s="23" t="s">
         <v>163</v>
       </c>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
+      <c r="B12" s="17"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3"/>
-      <c r="B13" s="23" t="s">
+      <c r="B13" s="22" t="s">
         <v>164</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="17"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="17"/>
+      <c r="G13" s="17"/>
+      <c r="H13" s="17"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="B14" s="23" t="s">
+      <c r="B14" s="22" t="s">
         <v>165</v>
       </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="18"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="17"/>
+      <c r="G14" s="17"/>
+      <c r="H14" s="17"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
-      <c r="B15" s="23" t="s">
+      <c r="B15" s="22" t="s">
         <v>166</v>
       </c>
-      <c r="C15" s="18"/>
-      <c r="D15" s="18"/>
-      <c r="E15" s="18"/>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
+      <c r="C15" s="17"/>
+      <c r="D15" s="17"/>
+      <c r="E15" s="17"/>
+      <c r="F15" s="17"/>
+      <c r="G15" s="17"/>
+      <c r="H15" s="17"/>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="24" t="s">
+      <c r="A17" s="23" t="s">
         <v>167</v>
       </c>
-      <c r="B17" s="18"/>
-      <c r="C17" s="18"/>
-      <c r="D17" s="18"/>
-      <c r="E17" s="18"/>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
+      <c r="B17" s="17"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="23" t="s">
+      <c r="B18" s="22" t="s">
         <v>168</v>
       </c>
-      <c r="C18" s="18"/>
-      <c r="D18" s="18"/>
-      <c r="E18" s="18"/>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
+      <c r="C18" s="17"/>
+      <c r="D18" s="17"/>
+      <c r="E18" s="17"/>
+      <c r="F18" s="17"/>
+      <c r="G18" s="17"/>
+      <c r="H18" s="17"/>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="23" t="s">
+      <c r="B19" s="22" t="s">
         <v>169</v>
       </c>
-      <c r="C19" s="18"/>
-      <c r="D19" s="18"/>
-      <c r="E19" s="18"/>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
+      <c r="C19" s="17"/>
+      <c r="D19" s="17"/>
+      <c r="E19" s="17"/>
+      <c r="F19" s="17"/>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17"/>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="23" t="s">
+      <c r="B20" s="22" t="s">
         <v>170</v>
       </c>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
+      <c r="C20" s="17"/>
+      <c r="D20" s="17"/>
+      <c r="E20" s="17"/>
+      <c r="F20" s="17"/>
+      <c r="G20" s="17"/>
+      <c r="H20" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="9">

--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\0304061\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A2E334-1F59-4799-9EFB-139A1607ECF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{BDDC8BC0-41D6-4ABA-8A9E-CEE4CCC72C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72C77FE-03F3-4ECB-BA7A-7160974D1D05}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BACKLOG" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="411" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="182">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -132,7 +132,7 @@
     <t>Implementar recebimento, extração, normalização e persistência dos dados de múltiplos currículos</t>
   </si>
   <si>
-    <t>Arthur</t>
+    <t>Artur</t>
   </si>
   <si>
     <t>#16</t>
@@ -210,24 +210,36 @@
     <t>--</t>
   </si>
   <si>
+    <t>#35</t>
+  </si>
+  <si>
     <t>T10</t>
   </si>
   <si>
     <t>Implementar interface para cadastrar, editar e excluir critérios de avaliação da vaga</t>
   </si>
   <si>
+    <t>#36</t>
+  </si>
+  <si>
     <t>T11</t>
   </si>
   <si>
     <t>Relacionar o perfil estruturado do candidato aos critérios de avaliação da vaga</t>
   </si>
   <si>
+    <t>#28</t>
+  </si>
+  <si>
     <t>T12</t>
   </si>
   <si>
     <t>Criar persistência e APIs para critérios de avaliação vinculados à vaga</t>
   </si>
   <si>
+    <t>#29</t>
+  </si>
+  <si>
     <t>T13</t>
   </si>
   <si>
@@ -237,18 +249,27 @@
     <t>Definir interface e fluxo para registro e consulta da entrevista do candidato</t>
   </si>
   <si>
+    <t>#32</t>
+  </si>
+  <si>
     <t>T14</t>
   </si>
   <si>
     <t>Implementar registro e consulta dos dados da entrevista</t>
   </si>
   <si>
+    <t>#33</t>
+  </si>
+  <si>
     <t>T15</t>
   </si>
   <si>
     <t>Criar persistência e APIs para registro e recuperação das entrevistas</t>
   </si>
   <si>
+    <t>#26</t>
+  </si>
+  <si>
     <t>T16</t>
   </si>
   <si>
@@ -258,18 +279,27 @@
     <t>Implementar atualização do perfil do candidato com informações provenientes da entrevista</t>
   </si>
   <si>
+    <t>#30</t>
+  </si>
+  <si>
     <t>T17</t>
   </si>
   <si>
     <t>Implementar edição e visualização do perfil enriquecido após a entrevista</t>
   </si>
   <si>
+    <t>#37</t>
+  </si>
+  <si>
     <t>T18</t>
   </si>
   <si>
     <t>Definir regras de consolidação entre informações do currículo e informações da entrevista</t>
   </si>
   <si>
+    <t>#38</t>
+  </si>
+  <si>
     <t>T19</t>
   </si>
   <si>
@@ -309,6 +339,9 @@
     <t>Implementar avaliação das características comportamentais conforme os critérios definidos para a vaga</t>
   </si>
   <si>
+    <t>#27</t>
+  </si>
+  <si>
     <t>T24</t>
   </si>
   <si>
@@ -553,19 +586,13 @@
   </si>
   <si>
     <t>Número da Issue criada no GitHub (ex.: #1, #2). Preencher após criar a Issue. Tarefas de Onda 2+ ficam com '--' até a onda ser ativada.</t>
-  </si>
-  <si>
-    <t>#26</t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -761,7 +788,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -780,6 +806,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1114,8 +1141,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K136"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetPr filterMode="1"/>
+  <dimension ref="A1:H136"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="3" width="10" customWidth="1"/>
@@ -1126,49 +1154,49 @@
     <col min="8" max="8" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="30" customHeight="1">
       <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="18" t="s">
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+    </row>
+    <row r="2" spans="1:8" ht="20.100000000000001" customHeight="1">
+      <c r="A2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="20" t="s">
+      <c r="B2" s="23"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17"/>
-      <c r="F2" s="18" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="17"/>
+      <c r="G2" s="23"/>
       <c r="H2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="36" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="19" t="s">
+    <row r="3" spans="1:8" ht="36" customHeight="1">
+      <c r="A3" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-    </row>
-    <row r="4" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="23"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="23"/>
+      <c r="H3" s="23"/>
+    </row>
+    <row r="4" spans="1:8" ht="24" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1194,7 +1222,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:8" ht="30" hidden="1">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -1220,7 +1248,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:8" ht="30" hidden="1">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -1246,7 +1274,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:8" ht="30" hidden="1">
       <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
@@ -1272,7 +1300,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="30" hidden="1">
       <c r="A8" s="14" t="s">
         <v>32</v>
       </c>
@@ -1298,7 +1326,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" ht="30" hidden="1">
       <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1324,7 +1352,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
@@ -1350,7 +1378,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" s="14" t="s">
         <v>44</v>
       </c>
@@ -1376,7 +1404,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" s="14" t="s">
         <v>47</v>
       </c>
@@ -1402,7 +1430,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:8" ht="30.75">
       <c r="A13" s="14" t="s">
         <v>51</v>
       </c>
@@ -1425,12 +1453,12 @@
         <v>55</v>
       </c>
       <c r="H13" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>52</v>
@@ -1442,7 +1470,7 @@
         <v>23</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>25</v>
@@ -1451,12 +1479,12 @@
         <v>55</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="14" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>52</v>
@@ -1468,17 +1496,21 @@
         <v>28</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G15" s="11"/>
-      <c r="H15" s="11"/>
-    </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G15" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="H15" s="11" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="18" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>52</v>
@@ -1490,7 +1522,7 @@
         <v>28</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>25</v>
@@ -1499,76 +1531,76 @@
         <v>30</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="18" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="14" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>55</v>
+        <v>20</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="14" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>25</v>
@@ -1577,24 +1609,24 @@
         <v>30</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="30.75">
       <c r="A20" s="14" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>25</v>
@@ -1603,24 +1635,24 @@
         <v>30</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15.95" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>25</v>
@@ -1629,24 +1661,24 @@
         <v>55</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="30.75">
       <c r="A22" s="14" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>19</v>
@@ -1655,27 +1687,24 @@
         <v>55</v>
       </c>
       <c r="H22" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="K22" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" hidden="1">
       <c r="A23" s="14" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>79</v>
+        <v>89</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>25</v>
@@ -1687,21 +1716,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" ht="30" hidden="1">
       <c r="A24" s="14" t="s">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C24" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E24" s="14" t="s">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="F24" s="14" t="s">
         <v>25</v>
@@ -1713,21 +1742,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" ht="30" hidden="1">
       <c r="A25" s="14" t="s">
-        <v>82</v>
+        <v>92</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C25" s="14" t="s">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>19</v>
@@ -1739,21 +1768,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" ht="15.95" hidden="1" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>84</v>
+        <v>94</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>19</v>
@@ -1765,47 +1794,47 @@
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" ht="30" hidden="1">
       <c r="A27" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B27" s="15" t="s">
         <v>87</v>
       </c>
-      <c r="B27" s="15" t="s">
-        <v>77</v>
-      </c>
       <c r="C27" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>88</v>
+        <v>98</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G27" s="13" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30" hidden="1">
       <c r="A28" s="14" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>25</v>
@@ -1817,21 +1846,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" ht="30" hidden="1">
       <c r="A29" s="14" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>93</v>
+        <v>104</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>19</v>
@@ -1843,21 +1872,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" ht="27" hidden="1" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>25</v>
@@ -1869,47 +1898,47 @@
         <v>55</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G31" s="13" t="s">
-        <v>55</v>
+        <v>30</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" s="14" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>101</v>
+        <v>112</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>25</v>
@@ -1921,21 +1950,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" ht="30" hidden="1">
       <c r="A33" s="14" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>25</v>
@@ -1947,21 +1976,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" ht="30" hidden="1">
       <c r="A34" s="14" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>25</v>
@@ -1973,21 +2002,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" ht="30" hidden="1">
       <c r="A35" s="14" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C35" s="14" t="s">
-        <v>100</v>
+        <v>111</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>25</v>
@@ -1999,21 +2028,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" ht="30" hidden="1">
       <c r="A36" s="14" t="s">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>110</v>
+        <v>121</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>19</v>
@@ -2025,21 +2054,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" ht="30" hidden="1">
       <c r="A37" s="14" t="s">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>25</v>
@@ -2051,21 +2080,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" hidden="1">
       <c r="A38" s="14" t="s">
-        <v>113</v>
+        <v>124</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>25</v>
@@ -2077,21 +2106,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" hidden="1">
       <c r="A39" s="14" t="s">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>19</v>
@@ -2103,21 +2132,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" hidden="1">
       <c r="A40" s="14" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F40" s="14" t="s">
         <v>19</v>
@@ -2129,21 +2158,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" hidden="1">
       <c r="A41" s="14" t="s">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>99</v>
+        <v>110</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>121</v>
+        <v>132</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>19</v>
@@ -2155,21 +2184,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" hidden="1">
       <c r="A42" s="14" t="s">
-        <v>122</v>
+        <v>133</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>19</v>
@@ -2181,21 +2210,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" hidden="1">
       <c r="A43" s="14" t="s">
-        <v>126</v>
+        <v>137</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="F43" s="14" t="s">
         <v>19</v>
@@ -2207,21 +2236,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" hidden="1">
       <c r="A44" s="14" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="F44" s="14" t="s">
         <v>19</v>
@@ -2233,21 +2262,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" ht="30" hidden="1">
       <c r="A45" s="14" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C45" s="14" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>19</v>
@@ -2259,21 +2288,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" ht="30" hidden="1">
       <c r="A46" s="14" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="F46" s="14" t="s">
         <v>25</v>
@@ -2285,21 +2314,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" hidden="1">
       <c r="A47" s="14" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>25</v>
@@ -2311,21 +2340,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" hidden="1">
       <c r="A48" s="14" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>19</v>
@@ -2337,21 +2366,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:8" hidden="1">
       <c r="A49" s="14" t="s">
-        <v>140</v>
+        <v>151</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>141</v>
+        <v>152</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>25</v>
@@ -2363,21 +2392,21 @@
         <v>55</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:8" ht="30" hidden="1">
       <c r="A50" s="14" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>123</v>
+        <v>134</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>25</v>
@@ -2389,7 +2418,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:8">
       <c r="A51" s="12"/>
       <c r="B51" s="12"/>
       <c r="C51" s="12"/>
@@ -2399,7 +2428,7 @@
       <c r="G51" s="13"/>
       <c r="H51" s="13"/>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:8">
       <c r="A52" s="12"/>
       <c r="B52" s="12"/>
       <c r="C52" s="12"/>
@@ -2409,7 +2438,7 @@
       <c r="G52" s="13"/>
       <c r="H52" s="13"/>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:8">
       <c r="A53" s="12"/>
       <c r="B53" s="12"/>
       <c r="C53" s="12"/>
@@ -2419,7 +2448,7 @@
       <c r="G53" s="13"/>
       <c r="H53" s="13"/>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:8">
       <c r="A54" s="12"/>
       <c r="B54" s="12"/>
       <c r="C54" s="12"/>
@@ -2429,7 +2458,7 @@
       <c r="G54" s="13"/>
       <c r="H54" s="13"/>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:8">
       <c r="A55" s="12"/>
       <c r="B55" s="12"/>
       <c r="C55" s="12"/>
@@ -2439,7 +2468,7 @@
       <c r="G55" s="13"/>
       <c r="H55" s="13"/>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:8">
       <c r="A56" s="12"/>
       <c r="B56" s="12"/>
       <c r="C56" s="12"/>
@@ -2449,7 +2478,7 @@
       <c r="G56" s="13"/>
       <c r="H56" s="13"/>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:8">
       <c r="A57" s="12"/>
       <c r="B57" s="12"/>
       <c r="C57" s="12"/>
@@ -2459,7 +2488,7 @@
       <c r="G57" s="13"/>
       <c r="H57" s="13"/>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:8">
       <c r="A58" s="12"/>
       <c r="B58" s="12"/>
       <c r="C58" s="12"/>
@@ -2469,7 +2498,7 @@
       <c r="G58" s="13"/>
       <c r="H58" s="13"/>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:8">
       <c r="A59" s="12"/>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
@@ -2479,7 +2508,7 @@
       <c r="G59" s="13"/>
       <c r="H59" s="13"/>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:8">
       <c r="A60" s="12"/>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
@@ -2489,7 +2518,7 @@
       <c r="G60" s="13"/>
       <c r="H60" s="13"/>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:8">
       <c r="A61" s="12"/>
       <c r="B61" s="12"/>
       <c r="C61" s="12"/>
@@ -2499,7 +2528,7 @@
       <c r="G61" s="13"/>
       <c r="H61" s="13"/>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:8">
       <c r="A62" s="12"/>
       <c r="B62" s="12"/>
       <c r="C62" s="12"/>
@@ -2509,7 +2538,7 @@
       <c r="G62" s="13"/>
       <c r="H62" s="13"/>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:8">
       <c r="A63" s="12"/>
       <c r="B63" s="12"/>
       <c r="C63" s="12"/>
@@ -2519,7 +2548,7 @@
       <c r="G63" s="13"/>
       <c r="H63" s="13"/>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:8">
       <c r="A64" s="12"/>
       <c r="B64" s="12"/>
       <c r="C64" s="12"/>
@@ -2529,7 +2558,7 @@
       <c r="G64" s="13"/>
       <c r="H64" s="13"/>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8">
       <c r="A65" s="12"/>
       <c r="B65" s="12"/>
       <c r="C65" s="12"/>
@@ -2539,7 +2568,7 @@
       <c r="G65" s="13"/>
       <c r="H65" s="13"/>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8">
       <c r="A66" s="12"/>
       <c r="B66" s="12"/>
       <c r="C66" s="12"/>
@@ -2549,7 +2578,7 @@
       <c r="G66" s="13"/>
       <c r="H66" s="13"/>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8">
       <c r="A67" s="12"/>
       <c r="B67" s="12"/>
       <c r="C67" s="12"/>
@@ -2559,7 +2588,7 @@
       <c r="G67" s="13"/>
       <c r="H67" s="13"/>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:8">
       <c r="A68" s="12"/>
       <c r="B68" s="12"/>
       <c r="C68" s="12"/>
@@ -2569,7 +2598,7 @@
       <c r="G68" s="13"/>
       <c r="H68" s="13"/>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:8">
       <c r="A69" s="12"/>
       <c r="B69" s="12"/>
       <c r="C69" s="12"/>
@@ -2579,7 +2608,7 @@
       <c r="G69" s="13"/>
       <c r="H69" s="13"/>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:8">
       <c r="A70" s="12"/>
       <c r="B70" s="12"/>
       <c r="C70" s="12"/>
@@ -2589,7 +2618,7 @@
       <c r="G70" s="13"/>
       <c r="H70" s="13"/>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:8">
       <c r="A71" s="12"/>
       <c r="B71" s="12"/>
       <c r="C71" s="12"/>
@@ -2599,7 +2628,7 @@
       <c r="G71" s="13"/>
       <c r="H71" s="13"/>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:8">
       <c r="A72" s="12"/>
       <c r="B72" s="12"/>
       <c r="C72" s="12"/>
@@ -2609,7 +2638,7 @@
       <c r="G72" s="13"/>
       <c r="H72" s="13"/>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:8">
       <c r="A73" s="12"/>
       <c r="B73" s="12"/>
       <c r="C73" s="12"/>
@@ -2619,7 +2648,7 @@
       <c r="G73" s="13"/>
       <c r="H73" s="13"/>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:8">
       <c r="A74" s="12"/>
       <c r="B74" s="12"/>
       <c r="C74" s="12"/>
@@ -2629,7 +2658,7 @@
       <c r="G74" s="13"/>
       <c r="H74" s="13"/>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:8">
       <c r="A75" s="12"/>
       <c r="B75" s="12"/>
       <c r="C75" s="12"/>
@@ -2639,7 +2668,7 @@
       <c r="G75" s="13"/>
       <c r="H75" s="13"/>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:8">
       <c r="A76" s="12"/>
       <c r="B76" s="12"/>
       <c r="C76" s="12"/>
@@ -2649,7 +2678,7 @@
       <c r="G76" s="13"/>
       <c r="H76" s="13"/>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:8">
       <c r="A77" s="12"/>
       <c r="B77" s="12"/>
       <c r="C77" s="12"/>
@@ -2659,7 +2688,7 @@
       <c r="G77" s="13"/>
       <c r="H77" s="13"/>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:8">
       <c r="A78" s="12"/>
       <c r="B78" s="12"/>
       <c r="C78" s="12"/>
@@ -2669,7 +2698,7 @@
       <c r="G78" s="13"/>
       <c r="H78" s="13"/>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:8">
       <c r="A79" s="12"/>
       <c r="B79" s="12"/>
       <c r="C79" s="12"/>
@@ -2679,7 +2708,7 @@
       <c r="G79" s="13"/>
       <c r="H79" s="13"/>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:8">
       <c r="A80" s="12"/>
       <c r="B80" s="12"/>
       <c r="C80" s="12"/>
@@ -2689,7 +2718,7 @@
       <c r="G80" s="13"/>
       <c r="H80" s="13"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8">
       <c r="A81" s="12"/>
       <c r="B81" s="12"/>
       <c r="C81" s="12"/>
@@ -2699,7 +2728,7 @@
       <c r="G81" s="13"/>
       <c r="H81" s="13"/>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8">
       <c r="A82" s="12"/>
       <c r="B82" s="12"/>
       <c r="C82" s="12"/>
@@ -2709,7 +2738,7 @@
       <c r="G82" s="13"/>
       <c r="H82" s="13"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8">
       <c r="A83" s="12"/>
       <c r="B83" s="12"/>
       <c r="C83" s="12"/>
@@ -2719,7 +2748,7 @@
       <c r="G83" s="13"/>
       <c r="H83" s="13"/>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:8">
       <c r="A84" s="12"/>
       <c r="B84" s="12"/>
       <c r="C84" s="12"/>
@@ -2729,7 +2758,7 @@
       <c r="G84" s="13"/>
       <c r="H84" s="13"/>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:8">
       <c r="A85" s="12"/>
       <c r="B85" s="12"/>
       <c r="C85" s="12"/>
@@ -2739,7 +2768,7 @@
       <c r="G85" s="13"/>
       <c r="H85" s="13"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8">
       <c r="A86" s="12"/>
       <c r="B86" s="12"/>
       <c r="C86" s="12"/>
@@ -2749,7 +2778,7 @@
       <c r="G86" s="13"/>
       <c r="H86" s="13"/>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:8">
       <c r="A87" s="12"/>
       <c r="B87" s="12"/>
       <c r="C87" s="12"/>
@@ -2759,7 +2788,7 @@
       <c r="G87" s="13"/>
       <c r="H87" s="13"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8">
       <c r="A88" s="12"/>
       <c r="B88" s="12"/>
       <c r="C88" s="12"/>
@@ -2769,7 +2798,7 @@
       <c r="G88" s="13"/>
       <c r="H88" s="13"/>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8">
       <c r="A89" s="12"/>
       <c r="B89" s="12"/>
       <c r="C89" s="12"/>
@@ -2779,7 +2808,7 @@
       <c r="G89" s="13"/>
       <c r="H89" s="13"/>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:8">
       <c r="A90" s="12"/>
       <c r="B90" s="12"/>
       <c r="C90" s="12"/>
@@ -2789,7 +2818,7 @@
       <c r="G90" s="13"/>
       <c r="H90" s="13"/>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8">
       <c r="A91" s="12"/>
       <c r="B91" s="12"/>
       <c r="C91" s="12"/>
@@ -2799,7 +2828,7 @@
       <c r="G91" s="13"/>
       <c r="H91" s="13"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8">
       <c r="A92" s="12"/>
       <c r="B92" s="12"/>
       <c r="C92" s="12"/>
@@ -2809,7 +2838,7 @@
       <c r="G92" s="13"/>
       <c r="H92" s="13"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8">
       <c r="A93" s="12"/>
       <c r="B93" s="12"/>
       <c r="C93" s="12"/>
@@ -2819,7 +2848,7 @@
       <c r="G93" s="13"/>
       <c r="H93" s="13"/>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8">
       <c r="A94" s="12"/>
       <c r="B94" s="12"/>
       <c r="C94" s="12"/>
@@ -2829,7 +2858,7 @@
       <c r="G94" s="13"/>
       <c r="H94" s="13"/>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8">
       <c r="A95" s="12"/>
       <c r="B95" s="12"/>
       <c r="C95" s="12"/>
@@ -2839,7 +2868,7 @@
       <c r="G95" s="13"/>
       <c r="H95" s="13"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8">
       <c r="A96" s="12"/>
       <c r="B96" s="12"/>
       <c r="C96" s="12"/>
@@ -2849,7 +2878,7 @@
       <c r="G96" s="13"/>
       <c r="H96" s="13"/>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:8">
       <c r="A97" s="12"/>
       <c r="B97" s="12"/>
       <c r="C97" s="12"/>
@@ -2859,7 +2888,7 @@
       <c r="G97" s="13"/>
       <c r="H97" s="13"/>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:8">
       <c r="A98" s="12"/>
       <c r="B98" s="12"/>
       <c r="C98" s="12"/>
@@ -2869,7 +2898,7 @@
       <c r="G98" s="13"/>
       <c r="H98" s="13"/>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:8">
       <c r="A99" s="12"/>
       <c r="B99" s="12"/>
       <c r="C99" s="12"/>
@@ -2879,7 +2908,7 @@
       <c r="G99" s="13"/>
       <c r="H99" s="13"/>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:8">
       <c r="A100" s="12"/>
       <c r="B100" s="12"/>
       <c r="C100" s="12"/>
@@ -2889,7 +2918,7 @@
       <c r="G100" s="13"/>
       <c r="H100" s="13"/>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:8">
       <c r="A101" s="12"/>
       <c r="B101" s="12"/>
       <c r="C101" s="12"/>
@@ -2899,7 +2928,7 @@
       <c r="G101" s="13"/>
       <c r="H101" s="13"/>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:8">
       <c r="A102" s="12"/>
       <c r="B102" s="12"/>
       <c r="C102" s="12"/>
@@ -2909,7 +2938,7 @@
       <c r="G102" s="13"/>
       <c r="H102" s="13"/>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:8">
       <c r="A103" s="12"/>
       <c r="B103" s="12"/>
       <c r="C103" s="12"/>
@@ -2919,7 +2948,7 @@
       <c r="G103" s="13"/>
       <c r="H103" s="13"/>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:8">
       <c r="A104" s="12"/>
       <c r="B104" s="12"/>
       <c r="C104" s="12"/>
@@ -2929,7 +2958,7 @@
       <c r="G104" s="13"/>
       <c r="H104" s="13"/>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:8">
       <c r="A105" s="12"/>
       <c r="B105" s="12"/>
       <c r="C105" s="12"/>
@@ -2939,7 +2968,7 @@
       <c r="G105" s="13"/>
       <c r="H105" s="13"/>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:8">
       <c r="A106" s="12"/>
       <c r="B106" s="12"/>
       <c r="C106" s="12"/>
@@ -2949,7 +2978,7 @@
       <c r="G106" s="13"/>
       <c r="H106" s="13"/>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:8">
       <c r="A107" s="12"/>
       <c r="B107" s="12"/>
       <c r="C107" s="12"/>
@@ -2959,7 +2988,7 @@
       <c r="G107" s="13"/>
       <c r="H107" s="13"/>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:8">
       <c r="A108" s="12"/>
       <c r="B108" s="12"/>
       <c r="C108" s="12"/>
@@ -2969,7 +2998,7 @@
       <c r="G108" s="13"/>
       <c r="H108" s="13"/>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:8">
       <c r="A109" s="12"/>
       <c r="B109" s="12"/>
       <c r="C109" s="12"/>
@@ -2979,7 +3008,7 @@
       <c r="G109" s="13"/>
       <c r="H109" s="13"/>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:8">
       <c r="A110" s="12"/>
       <c r="B110" s="12"/>
       <c r="C110" s="12"/>
@@ -2989,7 +3018,7 @@
       <c r="G110" s="13"/>
       <c r="H110" s="13"/>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:8">
       <c r="A111" s="12"/>
       <c r="B111" s="12"/>
       <c r="C111" s="12"/>
@@ -2999,7 +3028,7 @@
       <c r="G111" s="13"/>
       <c r="H111" s="13"/>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:8">
       <c r="A112" s="12"/>
       <c r="B112" s="12"/>
       <c r="C112" s="12"/>
@@ -3009,7 +3038,7 @@
       <c r="G112" s="13"/>
       <c r="H112" s="13"/>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:8">
       <c r="A113" s="12"/>
       <c r="B113" s="12"/>
       <c r="C113" s="12"/>
@@ -3019,7 +3048,7 @@
       <c r="G113" s="13"/>
       <c r="H113" s="13"/>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:8">
       <c r="A114" s="12"/>
       <c r="B114" s="12"/>
       <c r="C114" s="12"/>
@@ -3029,7 +3058,7 @@
       <c r="G114" s="13"/>
       <c r="H114" s="13"/>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:8">
       <c r="A115" s="12"/>
       <c r="B115" s="12"/>
       <c r="C115" s="12"/>
@@ -3039,7 +3068,7 @@
       <c r="G115" s="13"/>
       <c r="H115" s="13"/>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:8">
       <c r="A116" s="12"/>
       <c r="B116" s="12"/>
       <c r="C116" s="12"/>
@@ -3049,7 +3078,7 @@
       <c r="G116" s="13"/>
       <c r="H116" s="13"/>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:8">
       <c r="A117" s="12"/>
       <c r="B117" s="12"/>
       <c r="C117" s="12"/>
@@ -3059,7 +3088,7 @@
       <c r="G117" s="13"/>
       <c r="H117" s="13"/>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:8">
       <c r="A118" s="12"/>
       <c r="B118" s="12"/>
       <c r="C118" s="12"/>
@@ -3069,7 +3098,7 @@
       <c r="G118" s="13"/>
       <c r="H118" s="13"/>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:8">
       <c r="A119" s="12"/>
       <c r="B119" s="12"/>
       <c r="C119" s="12"/>
@@ -3079,7 +3108,7 @@
       <c r="G119" s="13"/>
       <c r="H119" s="13"/>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:8">
       <c r="A120" s="12"/>
       <c r="B120" s="12"/>
       <c r="C120" s="12"/>
@@ -3089,7 +3118,7 @@
       <c r="G120" s="13"/>
       <c r="H120" s="13"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:8">
       <c r="A121" s="12"/>
       <c r="B121" s="12"/>
       <c r="C121" s="12"/>
@@ -3099,7 +3128,7 @@
       <c r="G121" s="13"/>
       <c r="H121" s="13"/>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:8">
       <c r="A122" s="12"/>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -3109,7 +3138,7 @@
       <c r="G122" s="13"/>
       <c r="H122" s="13"/>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:8">
       <c r="A123" s="12"/>
       <c r="B123" s="12"/>
       <c r="C123" s="12"/>
@@ -3119,7 +3148,7 @@
       <c r="G123" s="13"/>
       <c r="H123" s="13"/>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:8">
       <c r="A124" s="12"/>
       <c r="B124" s="12"/>
       <c r="C124" s="12"/>
@@ -3129,7 +3158,7 @@
       <c r="G124" s="13"/>
       <c r="H124" s="13"/>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:8">
       <c r="A125" s="12"/>
       <c r="B125" s="12"/>
       <c r="C125" s="12"/>
@@ -3139,7 +3168,7 @@
       <c r="G125" s="13"/>
       <c r="H125" s="13"/>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:8">
       <c r="A126" s="12"/>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -3149,7 +3178,7 @@
       <c r="G126" s="13"/>
       <c r="H126" s="13"/>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:8">
       <c r="A127" s="12"/>
       <c r="B127" s="12"/>
       <c r="C127" s="12"/>
@@ -3159,7 +3188,7 @@
       <c r="G127" s="13"/>
       <c r="H127" s="13"/>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:8">
       <c r="A128" s="12"/>
       <c r="B128" s="12"/>
       <c r="C128" s="12"/>
@@ -3169,7 +3198,7 @@
       <c r="G128" s="13"/>
       <c r="H128" s="13"/>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:8">
       <c r="A129" s="12"/>
       <c r="B129" s="12"/>
       <c r="C129" s="12"/>
@@ -3179,7 +3208,7 @@
       <c r="G129" s="13"/>
       <c r="H129" s="13"/>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:8">
       <c r="A130" s="12"/>
       <c r="B130" s="12"/>
       <c r="C130" s="12"/>
@@ -3189,7 +3218,7 @@
       <c r="G130" s="13"/>
       <c r="H130" s="13"/>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:8">
       <c r="A131" s="12"/>
       <c r="B131" s="12"/>
       <c r="C131" s="12"/>
@@ -3199,7 +3228,7 @@
       <c r="G131" s="13"/>
       <c r="H131" s="13"/>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:8">
       <c r="A132" s="12"/>
       <c r="B132" s="12"/>
       <c r="C132" s="12"/>
@@ -3209,7 +3238,7 @@
       <c r="G132" s="13"/>
       <c r="H132" s="13"/>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:8">
       <c r="A133" s="12"/>
       <c r="B133" s="12"/>
       <c r="C133" s="12"/>
@@ -3219,7 +3248,7 @@
       <c r="G133" s="13"/>
       <c r="H133" s="13"/>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:8">
       <c r="A134" s="12"/>
       <c r="B134" s="12"/>
       <c r="C134" s="12"/>
@@ -3229,7 +3258,7 @@
       <c r="G134" s="13"/>
       <c r="H134" s="13"/>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:8">
       <c r="A135" s="12"/>
       <c r="B135" s="12"/>
       <c r="C135" s="12"/>
@@ -3239,7 +3268,7 @@
       <c r="G135" s="13"/>
       <c r="H135" s="13"/>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:8">
       <c r="A136" s="12"/>
       <c r="B136" s="12"/>
       <c r="C136" s="12"/>
@@ -3251,6 +3280,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:H50" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Onda 2"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H50">
       <sortCondition ref="B4:B50"/>
     </sortState>
@@ -3276,11 +3310,11 @@
       <formula>AND($B23&lt;&gt;"Onda 2", $H23="--")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
+  <dataValidations count="6">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D7 D9:D136" xr:uid="{EBD5ACE2-4F72-49FF-92DC-B66D019D738B}">
       <formula1>"Backend, Frontend, Design, QA, DevOps, Outro"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G136" xr:uid="{2A314C71-A3F7-4CC3-A8B8-816E48EDB30C}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G51:G136" xr:uid="{2A314C71-A3F7-4CC3-A8B8-816E48EDB30C}">
       <formula1>"Arthur, Lucas, Rafael, Willian"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5:B136" xr:uid="{58945E5D-A21B-492E-818C-2A764641538B}">
@@ -3292,6 +3326,9 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D8" xr:uid="{4A60EF7E-A204-4950-80FE-4AB3FD411CFA}">
       <formula1>"Backend, Frontend, Design, DevOps, Outro"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G5:G50" xr:uid="{845A3EB6-386A-45B6-91F9-B2C3E97FBA98}">
+      <formula1>"Artur, Lucas, Rafael, Willian"</formula1>
+    </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3300,191 +3337,191 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
     <col min="2" max="2" width="72" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="27.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="21" t="s">
-        <v>144</v>
-      </c>
-      <c r="B1" s="17"/>
-    </row>
-    <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="27.95" customHeight="1">
+      <c r="A1" s="20" t="s">
+        <v>155</v>
+      </c>
+      <c r="B1" s="23"/>
+    </row>
+    <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>145</v>
+        <v>156</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A12" s="23" t="s">
-        <v>163</v>
-      </c>
-      <c r="B12" s="17"/>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="22" t="s">
+        <v>174</v>
+      </c>
+      <c r="B12" s="23"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="23"/>
+    </row>
+    <row r="13" spans="1:8">
       <c r="A13" s="3"/>
-      <c r="B13" s="22" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="17"/>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="17"/>
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B13" s="21" t="s">
+        <v>175</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="23"/>
+    </row>
+    <row r="14" spans="1:8">
       <c r="A14" s="4"/>
-      <c r="B14" s="22" t="s">
-        <v>165</v>
-      </c>
-      <c r="C14" s="17"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="17"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="17"/>
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="21" t="s">
+        <v>176</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+    </row>
+    <row r="15" spans="1:8">
       <c r="A15" s="5"/>
-      <c r="B15" s="22" t="s">
-        <v>166</v>
-      </c>
-      <c r="C15" s="17"/>
-      <c r="D15" s="17"/>
-      <c r="E15" s="17"/>
-      <c r="F15" s="17"/>
-      <c r="G15" s="17"/>
-      <c r="H15" s="17"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A17" s="23" t="s">
-        <v>167</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="17"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="17"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="21" t="s">
+        <v>177</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="23"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" s="22" t="s">
+        <v>178</v>
+      </c>
+      <c r="B17" s="23"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="23"/>
+      <c r="F17" s="23"/>
+      <c r="G17" s="23"/>
+      <c r="H17" s="23"/>
+    </row>
+    <row r="18" spans="1:8">
       <c r="A18" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="22" t="s">
-        <v>168</v>
-      </c>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B18" s="21" t="s">
+        <v>179</v>
+      </c>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="23"/>
+      <c r="F18" s="23"/>
+      <c r="G18" s="23"/>
+      <c r="H18" s="23"/>
+    </row>
+    <row r="19" spans="1:8">
       <c r="A19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B19" s="22" t="s">
-        <v>169</v>
-      </c>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="17"/>
-      <c r="G19" s="17"/>
-      <c r="H19" s="17"/>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B19" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="23"/>
+      <c r="F19" s="23"/>
+      <c r="G19" s="23"/>
+      <c r="H19" s="23"/>
+    </row>
+    <row r="20" spans="1:8">
       <c r="A20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B20" s="22" t="s">
-        <v>170</v>
-      </c>
-      <c r="C20" s="17"/>
-      <c r="D20" s="17"/>
-      <c r="E20" s="17"/>
-      <c r="F20" s="17"/>
-      <c r="G20" s="17"/>
-      <c r="H20" s="17"/>
+      <c r="B20" s="21" t="s">
+        <v>181</v>
+      </c>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="23"/>
+      <c r="F20" s="23"/>
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -3504,23 +3541,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100069CEBA7CDA2B54A9B4CB9D08A57C2BE" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="4076db77eab4abd82fb5a98d0e08ed94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d90de4e3-1570-4373-8742-4e5b70768c2c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9ec4751c483cff2354015c975db5e37" ns3:_="">
     <xsd:import namespace="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
@@ -3728,38 +3748,31 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
 </file>
--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{BDDC8BC0-41D6-4ABA-8A9E-CEE4CCC72C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E72C77FE-03F3-4ECB-BA7A-7160974D1D05}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{BDDC8BC0-41D6-4ABA-8A9E-CEE4CCC72C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB2501E-25BE-4DC0-8F4B-3198353F61FD}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -207,109 +207,109 @@
     <t>Definir estrutura da interface para criação e edição dos critérios de avaliação de uma vaga</t>
   </si>
   <si>
+    <t>#35</t>
+  </si>
+  <si>
+    <t>T10</t>
+  </si>
+  <si>
+    <t>Implementar interface para cadastrar, editar e excluir critérios de avaliação da vaga</t>
+  </si>
+  <si>
+    <t>#36</t>
+  </si>
+  <si>
+    <t>T11</t>
+  </si>
+  <si>
+    <t>Relacionar o perfil estruturado do candidato aos critérios de avaliação da vaga</t>
+  </si>
+  <si>
+    <t>#28</t>
+  </si>
+  <si>
+    <t>T12</t>
+  </si>
+  <si>
+    <t>Criar persistência e APIs para critérios de avaliação vinculados à vaga</t>
+  </si>
+  <si>
+    <t>#29</t>
+  </si>
+  <si>
+    <t>T13</t>
+  </si>
+  <si>
+    <t>F11</t>
+  </si>
+  <si>
+    <t>Definir interface e fluxo para registro e consulta da entrevista do candidato</t>
+  </si>
+  <si>
+    <t>#32</t>
+  </si>
+  <si>
+    <t>T14</t>
+  </si>
+  <si>
+    <t>Implementar registro e consulta dos dados da entrevista</t>
+  </si>
+  <si>
+    <t>#33</t>
+  </si>
+  <si>
+    <t>T15</t>
+  </si>
+  <si>
+    <t>Criar persistência e APIs para registro e recuperação das entrevistas</t>
+  </si>
+  <si>
+    <t>#26</t>
+  </si>
+  <si>
+    <t>T16</t>
+  </si>
+  <si>
+    <t>F12</t>
+  </si>
+  <si>
+    <t>Implementar atualização do perfil do candidato com informações provenientes da entrevista</t>
+  </si>
+  <si>
+    <t>#30</t>
+  </si>
+  <si>
+    <t>T17</t>
+  </si>
+  <si>
+    <t>Implementar edição e visualização do perfil enriquecido após a entrevista</t>
+  </si>
+  <si>
+    <t>#37</t>
+  </si>
+  <si>
+    <t>T18</t>
+  </si>
+  <si>
+    <t>Definir regras de consolidação entre informações do currículo e informações da entrevista</t>
+  </si>
+  <si>
+    <t>#38</t>
+  </si>
+  <si>
+    <t>T19</t>
+  </si>
+  <si>
+    <t>Onda 3</t>
+  </si>
+  <si>
+    <t>F09</t>
+  </si>
+  <si>
+    <t>Criar spike técnico para avaliar integração com as plataformas externas previstas</t>
+  </si>
+  <si>
     <t>--</t>
-  </si>
-  <si>
-    <t>#35</t>
-  </si>
-  <si>
-    <t>T10</t>
-  </si>
-  <si>
-    <t>Implementar interface para cadastrar, editar e excluir critérios de avaliação da vaga</t>
-  </si>
-  <si>
-    <t>#36</t>
-  </si>
-  <si>
-    <t>T11</t>
-  </si>
-  <si>
-    <t>Relacionar o perfil estruturado do candidato aos critérios de avaliação da vaga</t>
-  </si>
-  <si>
-    <t>#28</t>
-  </si>
-  <si>
-    <t>T12</t>
-  </si>
-  <si>
-    <t>Criar persistência e APIs para critérios de avaliação vinculados à vaga</t>
-  </si>
-  <si>
-    <t>#29</t>
-  </si>
-  <si>
-    <t>T13</t>
-  </si>
-  <si>
-    <t>F11</t>
-  </si>
-  <si>
-    <t>Definir interface e fluxo para registro e consulta da entrevista do candidato</t>
-  </si>
-  <si>
-    <t>#32</t>
-  </si>
-  <si>
-    <t>T14</t>
-  </si>
-  <si>
-    <t>Implementar registro e consulta dos dados da entrevista</t>
-  </si>
-  <si>
-    <t>#33</t>
-  </si>
-  <si>
-    <t>T15</t>
-  </si>
-  <si>
-    <t>Criar persistência e APIs para registro e recuperação das entrevistas</t>
-  </si>
-  <si>
-    <t>#26</t>
-  </si>
-  <si>
-    <t>T16</t>
-  </si>
-  <si>
-    <t>F12</t>
-  </si>
-  <si>
-    <t>Implementar atualização do perfil do candidato com informações provenientes da entrevista</t>
-  </si>
-  <si>
-    <t>#30</t>
-  </si>
-  <si>
-    <t>T17</t>
-  </si>
-  <si>
-    <t>Implementar edição e visualização do perfil enriquecido após a entrevista</t>
-  </si>
-  <si>
-    <t>#37</t>
-  </si>
-  <si>
-    <t>T18</t>
-  </si>
-  <si>
-    <t>Definir regras de consolidação entre informações do currículo e informações da entrevista</t>
-  </si>
-  <si>
-    <t>#38</t>
-  </si>
-  <si>
-    <t>T19</t>
-  </si>
-  <si>
-    <t>Onda 3</t>
-  </si>
-  <si>
-    <t>F09</t>
-  </si>
-  <si>
-    <t>Criar spike técnico para avaliar integração com as plataformas externas previstas</t>
   </si>
   <si>
     <t>T20</t>
@@ -1141,7 +1141,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1222,7 +1221,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30" hidden="1">
+    <row r="5" spans="1:8" ht="30">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -1248,7 +1247,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30" hidden="1">
+    <row r="6" spans="1:8" ht="30">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -1274,7 +1273,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30" hidden="1">
+    <row r="7" spans="1:8" ht="30">
       <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
@@ -1300,7 +1299,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30" hidden="1">
+    <row r="8" spans="1:8" ht="30">
       <c r="A8" s="14" t="s">
         <v>32</v>
       </c>
@@ -1326,7 +1325,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30" hidden="1">
+    <row r="9" spans="1:8" ht="30">
       <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1352,7 +1351,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8" hidden="1">
+    <row r="10" spans="1:8">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
@@ -1378,7 +1377,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8" hidden="1">
+    <row r="11" spans="1:8">
       <c r="A11" s="14" t="s">
         <v>44</v>
       </c>
@@ -1404,7 +1403,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8" hidden="1">
+    <row r="12" spans="1:8">
       <c r="A12" s="14" t="s">
         <v>47</v>
       </c>
@@ -1450,15 +1449,15 @@
         <v>19</v>
       </c>
       <c r="G13" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>55</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="14" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B14" s="15" t="s">
         <v>52</v>
@@ -1470,21 +1469,21 @@
         <v>23</v>
       </c>
       <c r="E14" s="14" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="F14" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="H14" s="11" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="14" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" s="15" t="s">
         <v>52</v>
@@ -1496,7 +1495,7 @@
         <v>28</v>
       </c>
       <c r="E15" s="14" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F15" s="14" t="s">
         <v>25</v>
@@ -1505,12 +1504,12 @@
         <v>30</v>
       </c>
       <c r="H15" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1">
       <c r="A16" s="14" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B16" s="15" t="s">
         <v>52</v>
@@ -1522,7 +1521,7 @@
         <v>28</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="14" t="s">
         <v>25</v>
@@ -1531,24 +1530,24 @@
         <v>30</v>
       </c>
       <c r="H16" s="11" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1">
       <c r="A17" s="14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B17" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C17" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D17" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E17" s="14" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F17" s="14" t="s">
         <v>19</v>
@@ -1557,24 +1556,24 @@
         <v>20</v>
       </c>
       <c r="H17" s="11" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="14" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B18" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C18" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D18" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E18" s="14" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F18" s="14" t="s">
         <v>25</v>
@@ -1583,24 +1582,24 @@
         <v>20</v>
       </c>
       <c r="H18" s="11" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D19" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F19" s="14" t="s">
         <v>25</v>
@@ -1609,24 +1608,24 @@
         <v>30</v>
       </c>
       <c r="H19" s="11" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="20" spans="1:8" ht="30.75">
       <c r="A20" s="14" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B20" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D20" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F20" s="14" t="s">
         <v>25</v>
@@ -1635,96 +1634,96 @@
         <v>30</v>
       </c>
       <c r="H20" s="11" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="21" spans="1:8" ht="15.95" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B21" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D21" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E21" s="14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F21" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H21" s="13" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="22" spans="1:8" ht="30.75">
       <c r="A22" s="14" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B22" s="15" t="s">
         <v>52</v>
       </c>
       <c r="C22" s="14" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D22" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E22" s="14" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F22" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="H22" s="13" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" s="14" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="23" spans="1:8" hidden="1">
-      <c r="A23" s="14" t="s">
+      <c r="B23" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="B23" s="15" t="s">
+      <c r="C23" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="D23" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F23" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H23" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="30">
       <c r="A24" s="14" t="s">
         <v>90</v>
       </c>
       <c r="B24" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C24" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="D24" s="14" t="s">
         <v>28</v>
@@ -1736,21 +1735,21 @@
         <v>25</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30">
       <c r="A25" s="14" t="s">
         <v>92</v>
       </c>
       <c r="B25" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C25" s="14" t="s">
         <v>87</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>88</v>
       </c>
       <c r="D25" s="14" t="s">
         <v>23</v>
@@ -1762,18 +1761,18 @@
         <v>19</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" ht="15.95" hidden="1" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15.95" customHeight="1">
       <c r="A26" s="14" t="s">
         <v>94</v>
       </c>
       <c r="B26" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>95</v>
@@ -1788,18 +1787,18 @@
         <v>19</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="30">
       <c r="A27" s="14" t="s">
         <v>97</v>
       </c>
       <c r="B27" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>95</v>
@@ -1820,12 +1819,12 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="30" hidden="1">
+    <row r="28" spans="1:8" ht="30">
       <c r="A28" s="14" t="s">
         <v>100</v>
       </c>
       <c r="B28" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C28" s="14" t="s">
         <v>95</v>
@@ -1840,18 +1839,18 @@
         <v>25</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30">
       <c r="A29" s="14" t="s">
         <v>102</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="14" t="s">
         <v>103</v>
@@ -1866,18 +1865,18 @@
         <v>19</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" ht="27" hidden="1" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="27" customHeight="1">
       <c r="A30" s="14" t="s">
         <v>105</v>
       </c>
       <c r="B30" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>103</v>
@@ -1892,18 +1891,18 @@
         <v>25</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="14" t="s">
         <v>107</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C31" s="14" t="s">
         <v>103</v>
@@ -1924,7 +1923,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="32" spans="1:8" hidden="1">
+    <row r="32" spans="1:8">
       <c r="A32" s="14" t="s">
         <v>109</v>
       </c>
@@ -1944,13 +1943,13 @@
         <v>25</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30">
       <c r="A33" s="14" t="s">
         <v>113</v>
       </c>
@@ -1970,13 +1969,13 @@
         <v>25</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="30">
       <c r="A34" s="14" t="s">
         <v>115</v>
       </c>
@@ -1996,13 +1995,13 @@
         <v>25</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="30">
       <c r="A35" s="14" t="s">
         <v>117</v>
       </c>
@@ -2022,13 +2021,13 @@
         <v>25</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30">
       <c r="A36" s="14" t="s">
         <v>119</v>
       </c>
@@ -2048,13 +2047,13 @@
         <v>19</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="30">
       <c r="A37" s="14" t="s">
         <v>122</v>
       </c>
@@ -2074,13 +2073,13 @@
         <v>25</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
       <c r="A38" s="14" t="s">
         <v>124</v>
       </c>
@@ -2100,13 +2099,13 @@
         <v>25</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
       <c r="A39" s="14" t="s">
         <v>126</v>
       </c>
@@ -2126,13 +2125,13 @@
         <v>19</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
       <c r="A40" s="14" t="s">
         <v>129</v>
       </c>
@@ -2152,13 +2151,13 @@
         <v>19</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
       <c r="A41" s="14" t="s">
         <v>131</v>
       </c>
@@ -2178,13 +2177,13 @@
         <v>19</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
       <c r="A42" s="14" t="s">
         <v>133</v>
       </c>
@@ -2204,13 +2203,13 @@
         <v>19</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
       <c r="A43" s="14" t="s">
         <v>137</v>
       </c>
@@ -2230,13 +2229,13 @@
         <v>19</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" s="14" t="s">
         <v>139</v>
       </c>
@@ -2256,13 +2255,13 @@
         <v>19</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="30">
       <c r="A45" s="14" t="s">
         <v>141</v>
       </c>
@@ -2282,13 +2281,13 @@
         <v>19</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="30">
       <c r="A46" s="14" t="s">
         <v>144</v>
       </c>
@@ -2308,13 +2307,13 @@
         <v>25</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
       <c r="A47" s="14" t="s">
         <v>146</v>
       </c>
@@ -2334,13 +2333,13 @@
         <v>25</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
       <c r="A48" s="14" t="s">
         <v>148</v>
       </c>
@@ -2360,13 +2359,13 @@
         <v>19</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
       <c r="A49" s="14" t="s">
         <v>151</v>
       </c>
@@ -2386,13 +2385,13 @@
         <v>25</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="30" hidden="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="30">
       <c r="A50" s="14" t="s">
         <v>153</v>
       </c>
@@ -2412,10 +2411,10 @@
         <v>25</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>55</v>
+        <v>89</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3280,11 +3279,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:H50" xr:uid="{00000000-0009-0000-0000-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Onda 2"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H50">
       <sortCondition ref="B4:B50"/>
     </sortState>
@@ -3749,6 +3743,14 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
@@ -3757,22 +3759,14 @@
 </FormTemplates>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
 </file>
--- a/BACKLOG.xlsx
+++ b/BACKLOG.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lucas\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="13_ncr:1_{BDDC8BC0-41D6-4ABA-8A9E-CEE4CCC72C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFB2501E-25BE-4DC0-8F4B-3198353F61FD}"/>
+  <xr:revisionPtr revIDLastSave="47" documentId="13_ncr:1_{BDDC8BC0-41D6-4ABA-8A9E-CEE4CCC72C13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{11F78EB9-6E27-44B8-83A0-6223A007AC91}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="189">
   <si>
     <t>BACKLOG DO PRODUTO — Todas as Ondas até o MVP</t>
   </si>
@@ -309,13 +309,19 @@
     <t>Criar spike técnico para avaliar integração com as plataformas externas previstas</t>
   </si>
   <si>
+    <t>#41</t>
+  </si>
+  <si>
+    <t>T20</t>
+  </si>
+  <si>
+    <t>Implementar integração e importação de currículos a partir das plataformas externas selecionadas</t>
+  </si>
+  <si>
     <t>--</t>
   </si>
   <si>
-    <t>T20</t>
-  </si>
-  <si>
-    <t>Implementar integração e importação de currículos a partir das plataformas externas selecionadas</t>
+    <t>#42</t>
   </si>
   <si>
     <t>T21</t>
@@ -324,6 +330,9 @@
     <t>Implementar interface para iniciar a importação e acompanhar o resultado da integração</t>
   </si>
   <si>
+    <t>#43</t>
+  </si>
+  <si>
     <t>T22</t>
   </si>
   <si>
@@ -333,6 +342,9 @@
     <t>Definir apresentação dos critérios e resultados da avaliação comportamental</t>
   </si>
   <si>
+    <t>#44</t>
+  </si>
+  <si>
     <t>T23</t>
   </si>
   <si>
@@ -348,6 +360,9 @@
     <t>Implementar visualização dos resultados da avaliação comportamental por candidato</t>
   </si>
   <si>
+    <t>#45</t>
+  </si>
+  <si>
     <t>T25</t>
   </si>
   <si>
@@ -357,10 +372,16 @@
     <t>Definir interface para acompanhamento da adaptação técnica e comportamental do novo funcionário</t>
   </si>
   <si>
+    <t>#46</t>
+  </si>
+  <si>
     <t>T26</t>
   </si>
   <si>
     <t>Implementar registro e visualização do acompanhamento da adaptação do funcionário</t>
+  </si>
+  <si>
+    <t>#47</t>
   </si>
   <si>
     <t>T27</t>
@@ -1141,6 +1162,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:H136"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -1221,7 +1243,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="30">
+    <row r="5" spans="1:8" ht="30" hidden="1">
       <c r="A5" s="14" t="s">
         <v>14</v>
       </c>
@@ -1247,7 +1269,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="30">
+    <row r="6" spans="1:8" ht="30" hidden="1">
       <c r="A6" s="14" t="s">
         <v>22</v>
       </c>
@@ -1273,7 +1295,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="30">
+    <row r="7" spans="1:8" ht="30" hidden="1">
       <c r="A7" s="14" t="s">
         <v>27</v>
       </c>
@@ -1299,7 +1321,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="30">
+    <row r="8" spans="1:8" ht="30" hidden="1">
       <c r="A8" s="14" t="s">
         <v>32</v>
       </c>
@@ -1325,7 +1347,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:8" ht="30">
+    <row r="9" spans="1:8" ht="30" hidden="1">
       <c r="A9" s="14" t="s">
         <v>36</v>
       </c>
@@ -1351,7 +1373,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" hidden="1">
       <c r="A10" s="14" t="s">
         <v>41</v>
       </c>
@@ -1377,7 +1399,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" hidden="1">
       <c r="A11" s="14" t="s">
         <v>44</v>
       </c>
@@ -1403,7 +1425,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" hidden="1">
       <c r="A12" s="14" t="s">
         <v>47</v>
       </c>
@@ -1429,7 +1451,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="1:8" ht="30.75">
+    <row r="13" spans="1:8" ht="30.75" hidden="1">
       <c r="A13" s="14" t="s">
         <v>51</v>
       </c>
@@ -1455,7 +1477,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" hidden="1">
       <c r="A14" s="14" t="s">
         <v>56</v>
       </c>
@@ -1481,7 +1503,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" hidden="1">
       <c r="A15" s="14" t="s">
         <v>59</v>
       </c>
@@ -1507,7 +1529,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="18" customHeight="1">
+    <row r="16" spans="1:8" ht="18" hidden="1" customHeight="1">
       <c r="A16" s="14" t="s">
         <v>62</v>
       </c>
@@ -1533,7 +1555,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="18" customHeight="1">
+    <row r="17" spans="1:8" ht="18" hidden="1" customHeight="1">
       <c r="A17" s="14" t="s">
         <v>65</v>
       </c>
@@ -1559,7 +1581,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" hidden="1">
       <c r="A18" s="14" t="s">
         <v>69</v>
       </c>
@@ -1585,7 +1607,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" hidden="1">
       <c r="A19" s="14" t="s">
         <v>72</v>
       </c>
@@ -1611,7 +1633,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="30.75">
+    <row r="20" spans="1:8" ht="30.75" hidden="1">
       <c r="A20" s="14" t="s">
         <v>75</v>
       </c>
@@ -1637,7 +1659,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="15.95" customHeight="1">
+    <row r="21" spans="1:8" ht="15.95" hidden="1" customHeight="1">
       <c r="A21" s="14" t="s">
         <v>79</v>
       </c>
@@ -1663,7 +1685,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:8" ht="30.75">
+    <row r="22" spans="1:8" ht="30.75" hidden="1">
       <c r="A22" s="14" t="s">
         <v>82</v>
       </c>
@@ -1709,13 +1731,13 @@
         <v>25</v>
       </c>
       <c r="G23" s="13" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="H23" s="13" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="30">
+    <row r="24" spans="1:8" ht="30.75">
       <c r="A24" s="14" t="s">
         <v>90</v>
       </c>
@@ -1735,15 +1757,15 @@
         <v>25</v>
       </c>
       <c r="G24" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H24" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" ht="30">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="30.75">
       <c r="A25" s="14" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="B25" s="15" t="s">
         <v>86</v>
@@ -1755,59 +1777,59 @@
         <v>23</v>
       </c>
       <c r="E25" s="14" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F25" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G25" s="13" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="H25" s="13" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
     </row>
     <row r="26" spans="1:8" ht="15.95" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B26" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D26" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="F26" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G26" s="13" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="H26" s="13" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:8" ht="30">
       <c r="A27" s="14" t="s">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B27" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D27" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F27" s="14" t="s">
         <v>25</v>
@@ -1816,102 +1838,102 @@
         <v>30</v>
       </c>
       <c r="H27" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" ht="30">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="30.75">
       <c r="A28" s="14" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="B28" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="D28" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E28" s="14" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="F28" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G28" s="13" t="s">
-        <v>89</v>
+        <v>49</v>
       </c>
       <c r="H28" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="30">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="30.75">
       <c r="A29" s="14" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="B29" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C29" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D29" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E29" s="14" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="F29" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G29" s="13" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="H29" s="13" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
     </row>
     <row r="30" spans="1:8" ht="27" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="B30" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D30" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F30" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G30" s="13" t="s">
-        <v>89</v>
+        <v>20</v>
       </c>
       <c r="H30" s="13" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
     </row>
     <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="B31" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C31" s="14" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D31" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E31" s="14" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="F31" s="14" t="s">
         <v>25</v>
@@ -1920,501 +1942,501 @@
         <v>30</v>
       </c>
       <c r="H31" s="13" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" hidden="1">
       <c r="A32" s="14" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C32" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D32" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E32" s="14" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="F32" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G32" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H32" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="30" hidden="1">
       <c r="A33" s="14" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D33" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="F33" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G33" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H33" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="30" hidden="1">
       <c r="A34" s="14" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="B34" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D34" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="F34" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G34" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H34" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="30" hidden="1">
       <c r="A35" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>117</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>110</v>
-      </c>
       <c r="C35" s="14" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="D35" s="14" t="s">
         <v>33</v>
       </c>
       <c r="E35" s="14" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="F35" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G35" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H35" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="30" hidden="1">
       <c r="A36" s="14" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="B36" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C36" s="14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D36" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E36" s="14" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="F36" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G36" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H36" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="30" hidden="1">
       <c r="A37" s="14" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D37" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="F37" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G37" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H37" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" hidden="1">
       <c r="A38" s="14" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="B38" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C38" s="14" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="D38" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E38" s="14" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="F38" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G38" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H38" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="39" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" hidden="1">
       <c r="A39" s="14" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="B39" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C39" s="14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D39" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E39" s="14" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F39" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G39" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H39" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="40" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" hidden="1">
       <c r="A40" s="14" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="B40" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D40" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="F40" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G40" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H40" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" hidden="1">
       <c r="A41" s="14" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="D41" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="F41" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G41" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H41" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="42" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" hidden="1">
       <c r="A42" s="14" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="B42" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C42" s="14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D42" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E42" s="14" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="F42" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G42" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H42" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="43" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" hidden="1">
       <c r="A43" s="14" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C43" s="14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D43" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E43" s="14" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="F43" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G43" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H43" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" hidden="1">
       <c r="A44" s="14" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="B44" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="D44" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="F44" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G44" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H44" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="30" hidden="1">
       <c r="A45" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B45" s="15" t="s">
         <v>141</v>
       </c>
-      <c r="B45" s="15" t="s">
-        <v>134</v>
-      </c>
       <c r="C45" s="14" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D45" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="F45" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G45" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H45" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="46" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="30" hidden="1">
       <c r="A46" s="14" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="B46" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C46" s="14" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D46" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="F46" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G46" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H46" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" hidden="1">
       <c r="A47" s="14" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="D47" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="F47" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G47" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H47" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="48" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" hidden="1">
       <c r="A48" s="14" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="B48" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D48" s="14" t="s">
         <v>17</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="F48" s="14" t="s">
         <v>19</v>
       </c>
       <c r="G48" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H48" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="49" spans="1:8">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" hidden="1">
       <c r="A49" s="14" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D49" s="14" t="s">
         <v>23</v>
       </c>
       <c r="E49" s="14" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="F49" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G49" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H49" s="13" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="50" spans="1:8" ht="30">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="30" hidden="1">
       <c r="A50" s="14" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="B50" s="15" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C50" s="14" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="D50" s="14" t="s">
         <v>28</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="F50" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G50" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="H50" s="13" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
     </row>
     <row r="51" spans="1:8">
@@ -3279,6 +3301,11 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:H50" xr:uid="{00000000-0009-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Onda 3"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A5:H50">
       <sortCondition ref="B4:B50"/>
     </sortState>
@@ -3339,85 +3366,85 @@
   <sheetData>
     <row r="1" spans="1:8" ht="27.95" customHeight="1">
       <c r="A1" s="20" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="B1" s="23"/>
     </row>
     <row r="2" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A2" s="7" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A3" s="9" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
     </row>
     <row r="4" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A5" s="9" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A6" s="7" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A7" s="9" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
     </row>
     <row r="8" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A8" s="7" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
     </row>
     <row r="9" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A9" s="9" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:8" ht="39.950000000000003" customHeight="1">
       <c r="A10" s="7" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="22" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B12" s="23"/>
       <c r="C12" s="23"/>
@@ -3430,7 +3457,7 @@
     <row r="13" spans="1:8">
       <c r="A13" s="3"/>
       <c r="B13" s="21" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C13" s="23"/>
       <c r="D13" s="23"/>
@@ -3442,7 +3469,7 @@
     <row r="14" spans="1:8">
       <c r="A14" s="4"/>
       <c r="B14" s="21" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C14" s="23"/>
       <c r="D14" s="23"/>
@@ -3454,7 +3481,7 @@
     <row r="15" spans="1:8">
       <c r="A15" s="5"/>
       <c r="B15" s="21" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C15" s="23"/>
       <c r="D15" s="23"/>
@@ -3465,7 +3492,7 @@
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="22" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="B17" s="23"/>
       <c r="C17" s="23"/>
@@ -3480,7 +3507,7 @@
         <v>9</v>
       </c>
       <c r="B18" s="21" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C18" s="23"/>
       <c r="D18" s="23"/>
@@ -3494,7 +3521,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="21" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C19" s="23"/>
       <c r="D19" s="23"/>
@@ -3508,7 +3535,7 @@
         <v>13</v>
       </c>
       <c r="B20" s="21" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C20" s="23"/>
       <c r="D20" s="23"/>
@@ -3535,6 +3562,23 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100069CEBA7CDA2B54A9B4CB9D08A57C2BE" ma:contentTypeVersion="14" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="4076db77eab4abd82fb5a98d0e08ed94">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="d90de4e3-1570-4373-8742-4e5b70768c2c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c9ec4751c483cff2354015c975db5e37" ns3:_="">
     <xsd:import namespace="d90de4e3-1570-4373-8742-4e5b70768c2c"/>
@@ -3742,31 +3786,14 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="d90de4e3-1570-4373-8742-4e5b70768c2c" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E8C9EAED-E792-4EBD-8FE5-A88413F06C36}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0FA79B10-923E-46FD-992E-6B2FB513113C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F54BD295-47E6-4D5E-AB8C-AB6A369202DB}"/>
 </file>